--- a/工事担任者問題20260522.xlsx
+++ b/工事担任者問題20260522.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8754" uniqueCount="3055">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8754" uniqueCount="3056">
   <si>
     <t>ID</t>
   </si>
@@ -9446,6 +9446,9 @@
   </si>
   <si>
     <t>電子署名法の目的は「流通及び情報処理の促進を図り国民生活の向上及び国民経済の健全な発展に寄与すること」（A正）。電磁的記録が真正に成立したと推定されるのは「本人による電子署名が行われているとき（暗号化ではない）」（B誤）。</t>
+  </si>
+  <si>
+    <t>r6_1_g_q5_5.png</t>
   </si>
 </sst>
 </file>
@@ -9795,7 +9798,9 @@
   <dimension ref="A1:V502"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="22" width="7.6640625" style="1" customWidth="1"/>
+    <col min="1" max="17" width="7.6640625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="83.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="22" width="7.6640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="13.2" x14ac:dyDescent="0.2">
@@ -27601,7 +27606,7 @@
         <v>48</v>
       </c>
       <c r="R323" t="s">
-        <v>2110</v>
+        <v>2135</v>
       </c>
       <c r="U323" t="s">
         <v>2119</v>
@@ -27816,7 +27821,7 @@
         <v>36</v>
       </c>
       <c r="R327" t="s">
-        <v>2135</v>
+        <v>3055</v>
       </c>
       <c r="S327" t="s">
         <v>2136</v>

--- a/工事担任者問題20260522.xlsx
+++ b/工事担任者問題20260522.xlsx
@@ -646,7 +646,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>GE-PON,OLT,ONU,TDMA,LLID,DBA</t>
+          <t>GE-PON|GE-PON 工事担任者,OLT|OLT 工事担任者,ONU|ONU 工事担任者,TDMA|TDMA 工事担任者,LLID|LLID 工事担任者</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>IP-PBX,VoIPゲートウェイ,SIP,IPセントレックス</t>
+          <t>IP-PBX|IP-PBX 工事担任者,VoIPゲートウェイ|VoIPゲートウェイ 工事担任者,IPセントレックス|IPセントレックス 工事担任者</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>PoE,IEEE802.3at,PSE,PD</t>
+          <t>IEEE802.3at|IEEE802.3at 工事担任者,PSE|PSE PoE 工事担任者</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>レイヤ3スイッチ,RIP,OSPF,ルーティングプロトコル</t>
+          <t>レイヤ3スイッチ|レイヤ3スイッチ 工事担任者,RIP|RIP OSPF ルーティングプロトコル 工事担任者,OSPF|OSPF 工事担任者</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>SPD,バリスタ,過渡電圧抑制ダイオード,サージ防護</t>
+          <t>SPD|SPD 工事担任者,バリスタ|バリスタ SPD 工事担任者</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>10GBASE-LR,64B/66B,8B/10B,4B/5B</t>
+          <t>10GBASE-LR|10GBASE-LR 工事担任者,64B/66B|64B/66B 工事担任者</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>SS方式,PDS方式,PON,光ファイバ</t>
+          <t>SS方式|SS方式 光ファイバ 工事担任者,PDS方式|PDS方式 PON 工事担任者</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>HFC,FTTH,光ノード,同軸ケーブル</t>
+          <t>HFC|HFC 工事担任者,FTTH|FTTH 工事担任者</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>IPv6,IPv4,MTU,パケット分割,DF</t>
+          <t>IPv6|IPv6 パケット分割 工事担任者,IPv4|IPv4 DF パケット分割 工事担任者</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>EoMPLS,LER,MPLS,プリアンブル,FCS</t>
+          <t>EoMPLS|EoMPLS 工事担任者,LER|LER MPLS 工事担任者,MPLS|MPLS 工事担任者</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>バッファオーバフロー,スタック,DoS攻撃</t>
+          <t>バッファオーバフロー攻撃|バッファオーバフロー攻撃 工事担任者</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>PAP,CHAP,チャレンジ・レスポンス,シングルサインオン</t>
+          <t>CHAP|CHAP 工事担任者,PAP|PAP 工事担任者</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>TLS,HTTPS,SMTP,スニッフィング,暗号化</t>
+          <t>TLS|TLS 工事担任者,スニッフィング|スニッフィング 暗号化対策 工事担任者</t>
         </is>
       </c>
     </row>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>syslog,UDP,SNMP,ログ管理</t>
+          <t>syslog|syslog 工事担任者</t>
         </is>
       </c>
     </row>
@@ -1993,7 +1993,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>JIS Q 27001,ISMS,情報セキュリティ</t>
+          <t>JIS Q 27001|JIS Q 27001 工事担任者</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>挿入法,カットバック法,OTDR,挿入損失</t>
+          <t>挿入法|挿入法 光ファイバ損失 工事担任者,カットバック法|カットバック法 工事担任者,OTDR|OTDR 工事担任者</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>POF,アクリル樹脂,フッ素樹脂,プラスチック光ファイバ</t>
+          <t>POF|POF プラスチック光ファイバ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>OTDR法,後方散乱光,光ファイバ損失試験,JIS C 6823</t>
+          <t>OTDR法|OTDR法 工事担任者,JIS C 6823|JIS C 6823 工事担任者</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>T568B,RJ-45,UTPケーブル,心線配色</t>
+          <t>T568B|T568B 工事担任者</t>
         </is>
       </c>
     </row>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>インタコネクト,クラスE,水平ケーブル,JIS X 5150</t>
+          <t>JIS X 5150|JIS X 5150 水平ケーブル最大長 工事担任者</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>反射減衰量,挿入損失,JIS X 5150</t>
+          <t>JIS X 5150|JIS X 5150 反射減衰量 工事担任者</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>OTDR,ダイナミックレンジ,後方散乱光,パルスパワー</t>
+          <t>OTDR|OTDR ダイナミックレンジ 工事担任者,ダイナミックレンジ|ダイナミックレンジ OTDR 工事担任者</t>
         </is>
       </c>
     </row>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>全二重,半二重,CSMA/CD,衝突</t>
+          <t>CSMA/CD|CSMA/CD 工事担任者,全二重通信|全二重通信 CSMA/CD 衝突 工事担任者</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>施工計画書,現場代理人,監督員,工事管理</t>
+          <t>施工計画書|施工計画書 工事担任者</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>アローダイアグラム,クリティカルパス,トータルフロート,PERT</t>
+          <t>アローダイアグラム|アローダイアグラム 工事担任者,クリティカルパス|クリティカルパス 工事担任者,トータルフロート|トータルフロート 工事担任者</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>基礎的電気通信役務,電気通信事業法</t>
+          <t>基礎的電気通信役務|基礎的電気通信役務 電気通信事業法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>管理規程,電気通信事業法</t>
+          <t>管理規程|管理規程 電気通信事業法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>技術基準適合認定,登録認定機関,表示</t>
+          <t>技術基準適合認定|技術基準適合認定 工事担任者</t>
         </is>
       </c>
     </row>
@@ -3354,7 +3354,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>端末設備,技術基準,電気通信事業法</t>
+          <t>端末設備|端末設備 技術基準 工事担任者</t>
         </is>
       </c>
     </row>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>重要通信,緊急通信,電気通信事業法</t>
+          <t>重要通信|重要通信 電気通信事業法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -3555,7 +3555,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>工事担任者,資格者証,端末設備等</t>
+          <t>工事担任者資格|工事担任者 資格者証 端末設備</t>
         </is>
       </c>
     </row>
@@ -3655,7 +3655,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>資格者証,再交付,書換え交付</t>
+          <t>資格者証|資格者証 再交付 工事担任者</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>技術基準適合認定,認定番号,表示方法</t>
+          <t>技術基準適合認定番号|技術基準適合認定番号 工事担任者</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>有線電気通信法,総務大臣,立入検査</t>
+          <t>有線電気通信法|有線電気通信法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>有線電気通信設備,技術基準,有線電気通信法</t>
+          <t>有線電気通信設備令|有線電気通信設備令 工事担任者</t>
         </is>
       </c>
     </row>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>アナログ電話用設備,専用通信回線設備,端末設備等規則</t>
+          <t>アナログ電話用設備|アナログ電話用設備 端末設備等規則 工事担任者,専用通信回線設備|専用通信回線設備 工事担任者</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>分界点,端末設備,接続方式</t>
+          <t>分界点|分界点 端末設備 工事担任者</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>直流回路,アナログ電話用設備,交換設備</t>
+          <t>直流回路|直流回路 アナログ電話用設備 工事担任者</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>評価雑音電力,実効的雑音電力,端末設備等規則</t>
+          <t>評価雑音電力|評価雑音電力 工事担任者</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>識別符号,無線設備,端末設備</t>
+          <t>識別符号|識別符号 無線設備 工事担任者</t>
         </is>
       </c>
     </row>
@@ -4542,7 +4542,7 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>押しボタンダイヤル,ダイヤル番号,ミニマムポーズ</t>
+          <t>押しボタンダイヤル信号|押しボタンダイヤル信号 工事担任者,ミニマムポーズ|ミニマムポーズ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>絶縁抵抗,配線設備,有線電気通信設備令</t>
+          <t>絶縁抵抗|絶縁抵抗 配線設備 工事担任者</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>自動再発信,発信要求信号,アナログ電話端末</t>
+          <t>自動再発信|自動再発信 アナログ電話端末 工事担任者</t>
         </is>
       </c>
     </row>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>初期識別符号,アクセス制御,端末設備等規則</t>
+          <t>初期識別符号|初期識別符号 工事担任者</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>漏話減衰量,専用通信回線設備等端末,端末設備等規則</t>
+          <t>漏話減衰量|漏話減衰量 工事担任者</t>
         </is>
       </c>
     </row>
@@ -5033,7 +5033,7 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>架空電線,電柱,安全係数,有線電気通信設備令</t>
+          <t>架空電線|架空電線 電柱 工事担任者</t>
         </is>
       </c>
     </row>
@@ -5138,7 +5138,7 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>電線,有線電気通信法,強電流電線</t>
+          <t>有線電気通信法|有線電気通信法 電線 工事担任者</t>
         </is>
       </c>
     </row>
@@ -5227,7 +5227,7 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>屋内電線,強電流電線,離隔距離,有線電気通信設備令</t>
+          <t>屋内電線|屋内電線 強電流電線 離隔距離 工事担任者</t>
         </is>
       </c>
     </row>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>不正アクセス禁止法,アクセス制御機能</t>
+          <t>不正アクセス禁止法|不正アクセス禁止法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>電子署名法,電磁的記録,認証業務</t>
+          <t>電子署名法|電子署名法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -5509,7 +5509,7 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>10G-EPON,IEEE802.3av,XG-PON,XGS-PON,FEC,64B/66B</t>
+          <t>10G-EPON|10G-EPON 工事担任者,XGS-PON|XGS-PON 工事担任者,FEC|FEC 10G-EPON 工事担任者</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>SIPサーバ,レジストラ,プロキシサーバ,リダイレクトサーバ,UAC</t>
+          <t>SIPサーバ|SIPサーバ 工事担任者,レジストラ|レジストラ SIP 工事担任者,UAC|UAC SIP 工事担任者</t>
         </is>
       </c>
     </row>
@@ -5705,7 +5705,7 @@
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>PoE,IEEE802.3at,Type1,Class0,PSE</t>
+          <t>IEEE802.3at|IEEE802.3at Type1 工事担任者</t>
         </is>
       </c>
     </row>
@@ -5803,7 +5803,7 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>ZigBee,Bluetooth,無線PAN,IEEE802.15.4</t>
+          <t>ZigBee|ZigBee 工事担任者</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>フェライトコア,コモンモードチョークコイル,EMC,ノイズ対策</t>
+          <t>コモンモードチョークコイル|コモンモードチョークコイル 工事担任者,フェライトコア|フェライトコア EMC 工事担任者</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>NRZI,AMI,2値符号,3値符号,MLT-3</t>
+          <t>NRZI|NRZI 工事担任者,AMI|AMI 工事担任者</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>FTTB,VDSL,PDS方式,PON</t>
+          <t>FTTB|FTTB 工事担任者,VDSL|VDSL 工事担任者</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>IPv6,マルチキャスト,リンクローカル,ユニークローカル</t>
+          <t>IPv6|IPv6 マルチキャスト 工事担任者</t>
         </is>
       </c>
     </row>
@@ -6292,7 +6292,7 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>PLC,パケット損失,ジッタ,VoIP,ARQ</t>
+          <t>PLC|PLC パケット損失補間 工事担任者</t>
         </is>
       </c>
     </row>
@@ -6382,7 +6382,7 @@
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>IP-VPN,広域イーサネット,MPLS,レイヤ2,レイヤ3</t>
+          <t>IP-VPN|IP-VPN 工事担任者,広域イーサネット|広域イーサネット 工事担任者</t>
         </is>
       </c>
     </row>
@@ -6475,7 +6475,7 @@
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>TCPスキャン,SYN,ポートスキャン,ステルススキャン</t>
+          <t>TCPスキャン|TCP SYNスキャン 工事担任者</t>
         </is>
       </c>
     </row>
@@ -6575,7 +6575,7 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>RSA暗号,素因数分解,ブロック暗号,ストリーム暗号</t>
+          <t>RSA暗号|RSA暗号 工事担任者,ブロック暗号|ブロック暗号 ストリーム暗号 工事担任者</t>
         </is>
       </c>
     </row>
@@ -6676,7 +6676,7 @@
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>パケットフィルタリング,ファイアウォール,IPアドレス,ポート番号</t>
+          <t>パケットフィルタリング|パケットフィルタリング 工事担任者</t>
         </is>
       </c>
     </row>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>ペネトレーションテスト,脆弱性診断,セキュリティ評価</t>
+          <t>ペネトレーションテスト|ペネトレーションテスト 工事担任者</t>
         </is>
       </c>
     </row>
@@ -6869,7 +6869,7 @@
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>情報セキュリティ方針,JIS Q 27001,ISMS</t>
+          <t>JIS Q 27001|JIS Q 27001 工事担任者</t>
         </is>
       </c>
     </row>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>光導通試験,励振用光ファイバ,SI形,GI形,PINホトダイオード</t>
+          <t>光導通試験|光導通試験 工事担任者,PINホトダイオード|PINホトダイオード 工事担任者</t>
         </is>
       </c>
     </row>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>フリーアクセスフロア,OAフロア,不陸調整</t>
+          <t>フリーアクセスフロア|フリーアクセスフロア 工事担任者</t>
         </is>
       </c>
     </row>
@@ -7155,7 +7155,7 @@
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>PoE,オルタナティブA,オルタナティブB,給電ピン</t>
+          <t>PoEオルタナティブA|PoE オルタナティブA 工事担任者,PoEオルタナティブB|PoE オルタナティブB 工事担任者</t>
         </is>
       </c>
     </row>
@@ -7253,7 +7253,7 @@
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>プライベートIPアドレス,クラスA,クラスB,クラスC</t>
+          <t>プライベートIPアドレス|プライベートIPアドレス 工事担任者</t>
         </is>
       </c>
     </row>
@@ -7356,7 +7356,7 @@
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>クロスコネクト,クラスE,水平ケーブル,JIS X 5150</t>
+          <t>JIS X 5150|JIS X 5150 クロスコネクト 工事担任者</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>MPOコネクタ,多心光コネクタ,プッシュプル,データセンタ</t>
+          <t>MPOコネクタ|MPOコネクタ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -7554,7 +7554,7 @@
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>挿入損失法,カットバック法,OTDR,非破壊測定</t>
+          <t>挿入損失法|挿入損失法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -7652,7 +7652,7 @@
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>STP,IEEE802.1D,スパニングツリー,ループ防止</t>
+          <t>STP|STP IEEE802.1D 工事担任者,IEEE802.1D|IEEE802.1D 工事担任者</t>
         </is>
       </c>
     </row>
@@ -7752,7 +7752,7 @@
       </c>
       <c r="W76" t="inlineStr">
         <is>
-          <t>ヒストグラム,パレート図,管理図,QC7つ道具</t>
+          <t>ヒストグラム|ヒストグラム QC 工事担任者,パレート図|パレート図 工事担任者</t>
         </is>
       </c>
     </row>
@@ -7858,7 +7858,7 @@
       </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>クリティカルパス,トータルフロート,アローダイアグラム</t>
+          <t>クリティカルパス|クリティカルパス 工事担任者</t>
         </is>
       </c>
     </row>
@@ -7953,7 +7953,7 @@
       </c>
       <c r="W78" t="inlineStr">
         <is>
-          <t>業務改善命令,電気通信事業法,重要通信</t>
+          <t>業務改善命令|業務改善命令 電気通信事業法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -8053,7 +8053,7 @@
       </c>
       <c r="W79" t="inlineStr">
         <is>
-          <t>重要通信,緊急通信,選挙管理機関,天災</t>
+          <t>重要通信|重要通信 緊急通信 工事担任者</t>
         </is>
       </c>
     </row>
@@ -8145,7 +8145,7 @@
       </c>
       <c r="W80" t="inlineStr">
         <is>
-          <t>業務改善命令,重要通信,電気通信事業法</t>
+          <t>業務改善命令|業務改善命令 重要通信 工事担任者</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="W81" t="inlineStr">
         <is>
-          <t>管理規程,確実かつ安定的,電気通信事業法</t>
+          <t>管理規程|管理規程 確実かつ安定的 工事担任者</t>
         </is>
       </c>
     </row>
@@ -8326,7 +8326,7 @@
       </c>
       <c r="W82" t="inlineStr">
         <is>
-          <t>端末設備,接続請求,電波,電気通信事業法</t>
+          <t>端末設備接続拒否|端末設備 接続請求 電波 工事担任者</t>
         </is>
       </c>
     </row>
@@ -8431,7 +8431,7 @@
       </c>
       <c r="W83" t="inlineStr">
         <is>
-          <t>工事担任者,第二級アナログ通信,基本インタフェース,資格区分</t>
+          <t>第二級アナログ通信|第二級アナログ通信 工事担任者</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="W84" t="inlineStr">
         <is>
-          <t>専用設備,工事担任者,資格者証,技術基準</t>
+          <t>専用設備|専用設備 工事担任者不要 工事担任者</t>
         </is>
       </c>
     </row>
@@ -8625,7 +8625,7 @@
       </c>
       <c r="W85" t="inlineStr">
         <is>
-          <t>技術基準適合認定番号,IP電話用設備,認定番号</t>
+          <t>技術基準適合認定番号|技術基準適合認定番号 IP電話 工事担任者</t>
         </is>
       </c>
     </row>
@@ -8725,7 +8725,7 @@
       </c>
       <c r="W86" t="inlineStr">
         <is>
-          <t>本邦外,有線電気通信設備,総務大臣,有線電気通信法</t>
+          <t>有線電気通信法|有線電気通信法 本邦外 工事担任者</t>
         </is>
       </c>
     </row>
@@ -8817,7 +8817,7 @@
       </c>
       <c r="W87" t="inlineStr">
         <is>
-          <t>非常事態,有線電気通信法,通信確保</t>
+          <t>有線電気通信法|有線電気通信法 非常事態 工事担任者</t>
         </is>
       </c>
     </row>
@@ -8922,7 +8922,7 @@
       </c>
       <c r="W88" t="inlineStr">
         <is>
-          <t>総合デジタル通信用設備,専用通信回線設備,アナログ電話用設備,端末設備等規則</t>
+          <t>総合デジタル通信用設備|総合デジタル通信用設備 工事担任者,専用通信回線設備|専用通信回線設備 工事担任者</t>
         </is>
       </c>
     </row>
@@ -9021,7 +9021,7 @@
       </c>
       <c r="W89" t="inlineStr">
         <is>
-          <t>接地抵抗,絶縁耐力,端末設備等規則</t>
+          <t>接地抵抗|接地抵抗 端末設備 工事担任者,絶縁耐力試験|絶縁耐力試験 工事担任者</t>
         </is>
       </c>
     </row>
@@ -9113,7 +9113,7 @@
       </c>
       <c r="W90" t="inlineStr">
         <is>
-          <t>識別符号,無線設備,通信路</t>
+          <t>識別符号|識別符号 工事担任者</t>
         </is>
       </c>
     </row>
@@ -9212,7 +9212,7 @@
       </c>
       <c r="W91" t="inlineStr">
         <is>
-          <t>端末設備,事業用電気通信設備,識別機能,無線設備</t>
+          <t>識別機能|識別機能 事業用電気通信設備 工事担任者</t>
         </is>
       </c>
     </row>
@@ -9304,7 +9304,7 @@
       </c>
       <c r="W92" t="inlineStr">
         <is>
-          <t>制御チャネル,移動電話用設備,移動電話端末</t>
+          <t>制御チャネル|制御チャネル 工事担任者</t>
         </is>
       </c>
     </row>
@@ -9409,7 +9409,7 @@
       </c>
       <c r="W93" t="inlineStr">
         <is>
-          <t>絶縁抵抗,配線設備,有線電気通信設備令</t>
+          <t>絶縁抵抗|絶縁抵抗 直流200V 工事担任者</t>
         </is>
       </c>
     </row>
@@ -9514,7 +9514,7 @@
       </c>
       <c r="W94" t="inlineStr">
         <is>
-          <t>押しボタンダイヤル,ダイヤル番号,ミニマムポーズ</t>
+          <t>ダイヤル番号|ダイヤル番号 16種類 工事担任者</t>
         </is>
       </c>
     </row>
@@ -9608,7 +9608,7 @@
       </c>
       <c r="W95" t="inlineStr">
         <is>
-          <t>専用通信回線設備等端末,電気的条件,光学的条件,直流電圧</t>
+          <t>専用通信回線設備等端末|専用通信回線設備等端末 工事担任者</t>
         </is>
       </c>
     </row>
@@ -9700,7 +9700,7 @@
       </c>
       <c r="W96" t="inlineStr">
         <is>
-          <t>IPを使用する専用通信回線設備等端末,アクセス制御</t>
+          <t>アクセス制御|アクセス制御 専用通信回線 工事担任者</t>
         </is>
       </c>
     </row>
@@ -9789,7 +9789,7 @@
       </c>
       <c r="W97" t="inlineStr">
         <is>
-          <t>IP電話端末,発信,応答,通信終了</t>
+          <t>IP電話端末|IP電話端末 発着信 工事担任者</t>
         </is>
       </c>
     </row>
@@ -9889,7 +9889,7 @@
       </c>
       <c r="W98" t="inlineStr">
         <is>
-          <t>絶対レベル,有効電力,デシベル,端末設備等規則</t>
+          <t>絶対レベル|絶対レベル 工事担任者</t>
         </is>
       </c>
     </row>
@@ -9983,7 +9983,7 @@
       </c>
       <c r="W99" t="inlineStr">
         <is>
-          <t>架空電線,強電流電線,足場金具,有線電気通信設備令</t>
+          <t>足場金具|足場金具 架空電線 工事担任者</t>
         </is>
       </c>
     </row>
@@ -10080,7 +10080,7 @@
       </c>
       <c r="W100" t="inlineStr">
         <is>
-          <t>架空電線,鉄道横断,軌条面,有線電気通信設備令</t>
+          <t>架空電線|架空電線 鉄道横断 工事担任者</t>
         </is>
       </c>
     </row>
@@ -10172,7 +10172,7 @@
       </c>
       <c r="W101" t="inlineStr">
         <is>
-          <t>不正アクセス禁止法,アクセス管理者,アクセス制御機能</t>
+          <t>不正アクセス禁止法|不正アクセス禁止法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -10264,7 +10264,7 @@
       </c>
       <c r="W102" t="inlineStr">
         <is>
-          <t>電子署名法,認証業務,電磁的記録</t>
+          <t>電子署名法|電子署名法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -10362,7 +10362,7 @@
       </c>
       <c r="W103" t="inlineStr">
         <is>
-          <t>GE-PON,OLT,P2MPディスカバリ,マルチポイントMACコントロール</t>
+          <t>GE-PON|GE-PON 工事担任者,P2MPディスカバリ|P2MPディスカバリ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -10462,7 +10462,7 @@
       </c>
       <c r="W104" t="inlineStr">
         <is>
-          <t>IP-PBX,ハードウェアタイプ,ソフトウェアタイプ,IPセントレックス</t>
+          <t>IP-PBX|IP-PBX 工事担任者,IPセントレックス|IPセントレックス 工事担任者</t>
         </is>
       </c>
     </row>
@@ -10565,7 +10565,7 @@
       </c>
       <c r="W105" t="inlineStr">
         <is>
-          <t>MIMO,OFDM,空間分割多重,無線LAN</t>
+          <t>MIMO|MIMO 工事担任者,OFDM|OFDM 工事担任者</t>
         </is>
       </c>
     </row>
@@ -10658,7 +10658,7 @@
       </c>
       <c r="W106" t="inlineStr">
         <is>
-          <t>LPWA,LoRaWAN,SIGFOX,IoT,省電力通信</t>
+          <t>LPWA|LPWA 工事担任者,LoRaWAN|LoRaWAN 工事担任者</t>
         </is>
       </c>
     </row>
@@ -10751,7 +10751,7 @@
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>EMC,電磁エミッション,電磁障害,イミュニティ,JIS C 60050</t>
+          <t>電磁エミッション|電磁エミッション EMC 工事担任者</t>
         </is>
       </c>
     </row>
@@ -10844,7 +10844,7 @@
       </c>
       <c r="W108" t="inlineStr">
         <is>
-          <t>SS方式,シングルスター,PDS方式,PON,光ファイバ</t>
+          <t>SS方式|SS方式 工事担任者,PDS方式|PDS方式 工事担任者</t>
         </is>
       </c>
     </row>
@@ -10942,7 +10942,7 @@
       </c>
       <c r="W109" t="inlineStr">
         <is>
-          <t>1000BASE-T,8B1Q4,4D-PAM5,符号化,UTP</t>
+          <t>8B1Q4|8B1Q4 工事担任者</t>
         </is>
       </c>
     </row>
@@ -11032,7 +11032,7 @@
       </c>
       <c r="W110" t="inlineStr">
         <is>
-          <t>MACアドレス,NIC,FCS,MACフレーム</t>
+          <t>MACアドレス|MACアドレス 工事担任者,FCS|FCS MACフレーム 工事担任者</t>
         </is>
       </c>
     </row>
@@ -11125,7 +11125,7 @@
       </c>
       <c r="W111" t="inlineStr">
         <is>
-          <t>トンネリング,デュアルスタック,IPv4,IPv6,カプセル化</t>
+          <t>トンネリング|トンネリング IPv6 工事担任者,デュアルスタック|デュアルスタック 工事担任者</t>
         </is>
       </c>
     </row>
@@ -11218,7 +11218,7 @@
       </c>
       <c r="W112" t="inlineStr">
         <is>
-          <t>EoMPLS,LER,MPLS,L2ヘッダ,プリアンブル</t>
+          <t>EoMPLS|EoMPLS 工事担任者,LER|LER MPLS 工事担任者,MPLS|MPLS 工事担任者</t>
         </is>
       </c>
     </row>
@@ -11315,7 +11315,7 @@
       </c>
       <c r="W113" t="inlineStr">
         <is>
-          <t>スマーフ攻撃,DoS,ICMP,ブロードキャスト,IPスプーフィング</t>
+          <t>スマーフ攻撃|スマーフ攻撃 工事担任者</t>
         </is>
       </c>
     </row>
@@ -11409,7 +11409,7 @@
       </c>
       <c r="W114" t="inlineStr">
         <is>
-          <t>認証局,CA,デジタル証明書,公開鍵,秘密鍵</t>
+          <t>認証局|認証局 デジタル証明書 工事担任者</t>
         </is>
       </c>
     </row>
@@ -11511,7 +11511,7 @@
       </c>
       <c r="W115" t="inlineStr">
         <is>
-          <t>バッファオーバフロー,スタック,脆弱性</t>
+          <t>バッファオーバフロー攻撃|バッファオーバフロー攻撃 工事担任者</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>デフォルトアカウント,アカウント管理,セキュリティ</t>
+          <t>デフォルトアカウント|デフォルトアカウント 工事担任者</t>
         </is>
       </c>
     </row>
@@ -11703,7 +11703,7 @@
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>リスクマネジメント,残留リスク,リスク低減,ISMS</t>
+          <t>残留リスク|残留リスク ISMS 工事担任者</t>
         </is>
       </c>
     </row>
@@ -11806,7 +11806,7 @@
       </c>
       <c r="W118" t="inlineStr">
         <is>
-          <t>挿入法,カットバック法,挿入損失,光コネクタ,JIS C 6823</t>
+          <t>挿入法|挿入法 工事担任者,カットバック法|カットバック法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -11882,7 +11882,7 @@
       </c>
       <c r="W119" t="inlineStr">
         <is>
-          <t>JIS C 0303,図記号,複合アウトレット,情報用アウトレット</t>
+          <t>JIS C 0303|JIS C 0303 工事担任者</t>
         </is>
       </c>
     </row>
@@ -11977,7 +11977,7 @@
       </c>
       <c r="W120" t="inlineStr">
         <is>
-          <t>OTDR法,後方散乱光,光ファイバ損失,JIS C 6823</t>
+          <t>OTDR法|OTDR法 工事担任者,JIS C 6823|JIS C 6823 工事担任者</t>
         </is>
       </c>
     </row>
@@ -12070,7 +12070,7 @@
       </c>
       <c r="W121" t="inlineStr">
         <is>
-          <t>T568B,RJ-45,UTPケーブル,心線配色</t>
+          <t>T568B|T568B 工事担任者</t>
         </is>
       </c>
     </row>
@@ -12168,7 +12168,7 @@
       </c>
       <c r="W122" t="inlineStr">
         <is>
-          <t>インタコネクト,クラスE,水平ケーブル,JIS X 5150</t>
+          <t>JIS X 5150|JIS X 5150 工事担任者</t>
         </is>
       </c>
     </row>
@@ -12271,7 +12271,7 @@
       </c>
       <c r="W123" t="inlineStr">
         <is>
-          <t>OTDR,ダミー光ファイバ,測定不能領域,後方散乱光</t>
+          <t>OTDR|OTDR ダミー光ファイバ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -12369,7 +12369,7 @@
       </c>
       <c r="W124" t="inlineStr">
         <is>
-          <t>FASコネクタ,単心光コネクタ,ドロップ光ファイバ,架空クロージャ</t>
+          <t>FASコネクタ|FASコネクタ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -12462,7 +12462,7 @@
       </c>
       <c r="W125" t="inlineStr">
         <is>
-          <t>細径インドア光ケーブル,低摩擦,集合住宅,光配線</t>
+          <t>細径インドア光ケーブル|細径インドア光ケーブル 工事担任者</t>
         </is>
       </c>
     </row>
@@ -12563,7 +12563,7 @@
       </c>
       <c r="W126" t="inlineStr">
         <is>
-          <t>工程管理,出来形管理,施工管理,品質管理</t>
+          <t>工程管理|工程管理 出来形管理 工事担任者,出来形管理|出来形管理 工事担任者</t>
         </is>
       </c>
     </row>
@@ -12669,7 +12669,7 @@
       </c>
       <c r="W127" t="inlineStr">
         <is>
-          <t>アローダイアグラム,クリティカルパス,トータルフロート,PERT</t>
+          <t>アローダイアグラム|アローダイアグラム 工事担任者,クリティカルパス|クリティカルパス 工事担任者</t>
         </is>
       </c>
     </row>
@@ -12765,7 +12765,7 @@
       </c>
       <c r="W128" t="inlineStr">
         <is>
-          <t>資格者証,工事担任者,罰金,養成課程,電気通信事業法</t>
+          <t>資格者証|資格者証 工事担任者</t>
         </is>
       </c>
     </row>
@@ -12860,7 +12860,7 @@
       </c>
       <c r="W129" t="inlineStr">
         <is>
-          <t>自営電気通信設備,接続拒否,技術基準,電気通信事業法</t>
+          <t>自営電気通信設備|自営電気通信設備 接続拒否 工事担任者</t>
         </is>
       </c>
     </row>
@@ -12955,7 +12955,7 @@
       </c>
       <c r="W130" t="inlineStr">
         <is>
-          <t>管理規程,基礎的電気通信役務,届出,電気通信事業法</t>
+          <t>管理規程|管理規程 届出 工事担任者</t>
         </is>
       </c>
     </row>
@@ -13053,7 +13053,7 @@
       </c>
       <c r="W131" t="inlineStr">
         <is>
-          <t>技術基準適合認定,表示,電気通信事業法</t>
+          <t>技術基準適合認定|技術基準適合認定 工事担任者</t>
         </is>
       </c>
     </row>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="W132" t="inlineStr">
         <is>
-          <t>重要通信,緊急通信,公共の利益,電気通信事業法</t>
+          <t>重要通信|重要通信 人命安全 工事担任者</t>
         </is>
       </c>
     </row>
@@ -13241,7 +13241,7 @@
       </c>
       <c r="W133" t="inlineStr">
         <is>
-          <t>工事担任者,第一級デジタル通信,第一級アナログ通信,資格区分</t>
+          <t>第一級デジタル通信|第一級デジタル通信 工事担任者,第一級アナログ通信|第一級アナログ通信 工事担任者</t>
         </is>
       </c>
     </row>
@@ -13335,7 +13335,7 @@
       </c>
       <c r="W134" t="inlineStr">
         <is>
-          <t>資格者証,再交付,返納,写真</t>
+          <t>資格者証|資格者証 再交付 返納 工事担任者</t>
         </is>
       </c>
     </row>
@@ -13429,7 +13429,7 @@
       </c>
       <c r="W135" t="inlineStr">
         <is>
-          <t>技術基準適合認定番号,移動電話用設備,総合デジタル通信用設備,認定番号</t>
+          <t>技術基準適合認定番号|技術基準適合認定番号 工事担任者</t>
         </is>
       </c>
     </row>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="W136" t="inlineStr">
         <is>
-          <t>有線電気通信法,総務大臣,報告,立入検査</t>
+          <t>有線電気通信法|有線電気通信法 立入検査 工事担任者</t>
         </is>
       </c>
     </row>
@@ -13618,7 +13618,7 @@
       </c>
       <c r="W137" t="inlineStr">
         <is>
-          <t>有線電気通信設備,設置の場所,変更届,2週間前</t>
+          <t>有線電気通信設備令|有線電気通信設備令 変更届 工事担任者</t>
         </is>
       </c>
     </row>
@@ -13718,7 +13718,7 @@
       </c>
       <c r="W138" t="inlineStr">
         <is>
-          <t>IP電話端末,IP電話用設備,絶対レベル,有効電力,端末設備等規則</t>
+          <t>IP電話端末|IP電話端末 工事担任者,絶対レベル|絶対レベル 工事担任者</t>
         </is>
       </c>
     </row>
@@ -13817,7 +13817,7 @@
       </c>
       <c r="W139" t="inlineStr">
         <is>
-          <t>通話機能,音響衝撃,鳴音,端末設備等規則</t>
+          <t>音響衝撃|音響衝撃 端末設備 工事担任者</t>
         </is>
       </c>
     </row>
@@ -13919,7 +13919,7 @@
       </c>
       <c r="W140" t="inlineStr">
         <is>
-          <t>配線設備,絶縁抵抗,直流200V,1MΩ</t>
+          <t>配線設備|配線設備 絶縁抵抗 工事担任者</t>
         </is>
       </c>
     </row>
@@ -14013,7 +14013,7 @@
       </c>
       <c r="W141" t="inlineStr">
         <is>
-          <t>識別符号,無線設備,呼出符号,空き周波数</t>
+          <t>識別符号|識別符号 空き周波数 工事担任者</t>
         </is>
       </c>
     </row>
@@ -14115,7 +14115,7 @@
       </c>
       <c r="W142" t="inlineStr">
         <is>
-          <t>絶縁抵抗,使用電圧,300V,0.4MΩ,0.2MΩ</t>
+          <t>絶縁抵抗|絶縁抵抗 使用電圧 工事担任者</t>
         </is>
       </c>
     </row>
@@ -14215,7 +14215,7 @@
       </c>
       <c r="W143" t="inlineStr">
         <is>
-          <t>移動電話端末,発信要求信号,漏話減衰量,1500Hz</t>
+          <t>移動電話端末|移動電話端末 発信 工事担任者,漏話減衰量|漏話減衰量 工事担任者</t>
         </is>
       </c>
     </row>
@@ -14320,7 +14320,7 @@
       </c>
       <c r="W144" t="inlineStr">
         <is>
-          <t>押しボタンダイヤル,信号送出時間,ミニマムポーズ,50ms</t>
+          <t>信号送出時間|信号送出時間 ミニマムポーズ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -14419,7 +14419,7 @@
       </c>
       <c r="W145" t="inlineStr">
         <is>
-          <t>分界点,接地抵抗,100オーム,端末設備</t>
+          <t>分界点|分界点 接地抵抗 工事担任者</t>
         </is>
       </c>
     </row>
@@ -14516,7 +14516,7 @@
       </c>
       <c r="W146" t="inlineStr">
         <is>
-          <t>IP電話端末,通信終了メッセージ,2分以内,応答確認</t>
+          <t>IP電話端末|IP電話端末 通信終了 工事担任者</t>
         </is>
       </c>
     </row>
@@ -14605,7 +14605,7 @@
       </c>
       <c r="W147" t="inlineStr">
         <is>
-          <t>総合デジタル通信用設備,自動再発信,チャネル切断</t>
+          <t>自動再発信|自動再発信 総合デジタル 工事担任者</t>
         </is>
       </c>
     </row>
@@ -14705,7 +14705,7 @@
       </c>
       <c r="W148" t="inlineStr">
         <is>
-          <t>架空電線,建造物,離隔距離,30センチメートル,有線電気通信設備令</t>
+          <t>架空電線|架空電線 建造物 離隔距離 工事担任者</t>
         </is>
       </c>
     </row>
@@ -14802,7 +14802,7 @@
       </c>
       <c r="W149" t="inlineStr">
         <is>
-          <t>強電流電線,重畳,分離,有線電気通信設備令</t>
+          <t>強電流電線|強電流電線 重畳 工事担任者</t>
         </is>
       </c>
     </row>
@@ -14899,7 +14899,7 @@
       </c>
       <c r="W150" t="inlineStr">
         <is>
-          <t>横断歩道橋,架空電線,3メートル,有線電気通信設備令</t>
+          <t>架空電線|架空電線 横断歩道橋 工事担任者</t>
         </is>
       </c>
     </row>
@@ -14988,7 +14988,7 @@
       </c>
       <c r="W151" t="inlineStr">
         <is>
-          <t>不正アクセス禁止法,アクセス管理者,アクセス制御機能</t>
+          <t>不正アクセス禁止法|不正アクセス禁止法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="W152" t="inlineStr">
         <is>
-          <t>電子署名法,特定認証業務,電磁的記録,電子署名</t>
+          <t>特定認証業務|特定認証業務 電子署名法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -15180,7 +15180,7 @@
       </c>
       <c r="W153" t="inlineStr">
         <is>
-          <t>10G-EPON,IEEE802.3av,XGS-PON,FEC,64B/66B</t>
+          <t>10G-EPON|10G-EPON 工事担任者,XGS-PON|XGS-PON 工事担任者</t>
         </is>
       </c>
     </row>
@@ -15278,7 +15278,7 @@
       </c>
       <c r="W154" t="inlineStr">
         <is>
-          <t>カットアンドスルー,ストアアンドフォワード,イーサネットスイッチ</t>
+          <t>カットアンドスルー|カットアンドスルー 工事担任者</t>
         </is>
       </c>
     </row>
@@ -15376,7 +15376,7 @@
       </c>
       <c r="W155" t="inlineStr">
         <is>
-          <t>IEEE802.3bt,Type4,Class8,PoE,90W</t>
+          <t>IEEE802.3bt|IEEE802.3bt 工事担任者</t>
         </is>
       </c>
     </row>
@@ -15469,7 +15469,7 @@
       </c>
       <c r="W156" t="inlineStr">
         <is>
-          <t>IEEE802.11n,ブロックACK,MIMO,フレーム集約</t>
+          <t>ブロックACK|ブロックACK IEEE802.11n 工事担任者</t>
         </is>
       </c>
     </row>
@@ -15562,7 +15562,7 @@
       </c>
       <c r="W157" t="inlineStr">
         <is>
-          <t>SPD,バリスタ,過渡電圧抑制ダイオード,サージ防護</t>
+          <t>SPD|SPD 工事担任者</t>
         </is>
       </c>
     </row>
@@ -15655,7 +15655,7 @@
       </c>
       <c r="W158" t="inlineStr">
         <is>
-          <t>NRZI,AMI,MLT-3,PAM-5,2値符号</t>
+          <t>NRZI|NRZI 工事担任者,AMI|AMI 工事担任者</t>
         </is>
       </c>
     </row>
@@ -15751,7 +15751,7 @@
       </c>
       <c r="W159" t="inlineStr">
         <is>
-          <t>SS方式,HFC,PDS方式,PON,光ファイバ</t>
+          <t>SS方式|SS方式 工事担任者,HFC|HFC 工事担任者</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="W160" t="inlineStr">
         <is>
-          <t>IaaS,PaaS,SaaS,クラウドサービス</t>
+          <t>IaaS|IaaS PaaS SaaS 工事担任者</t>
         </is>
       </c>
     </row>
@@ -15952,7 +15952,7 @@
       </c>
       <c r="W161" t="inlineStr">
         <is>
-          <t>ジッタバッファ,揺らぎ吸収,VoIP,音声品質</t>
+          <t>ジッタバッファ|ジッタバッファ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -16047,7 +16047,7 @@
       </c>
       <c r="W162" t="inlineStr">
         <is>
-          <t>EoMPLS,LER,MPLS,ラベルスイッチング,ルーティング</t>
+          <t>EoMPLS|EoMPLS 工事担任者,LER|LER 工事担任者,LSR|LSR MPLS 工事担任者</t>
         </is>
       </c>
     </row>
@@ -16145,7 +16145,7 @@
       </c>
       <c r="W163" t="inlineStr">
         <is>
-          <t>SEOポイズニング,不正Webサイト,検索エンジン</t>
+          <t>SEOポイズニング|SEOポイズニング 工事担任者</t>
         </is>
       </c>
     </row>
@@ -16241,7 +16241,7 @@
       </c>
       <c r="W164" t="inlineStr">
         <is>
-          <t>チャレンジ・レスポンス,CHAP,ハイブリッド方式,認証</t>
+          <t>チャレンジ・レスポンス|チャレンジ・レスポンス 工事担任者</t>
         </is>
       </c>
     </row>
@@ -16336,7 +16336,7 @@
       </c>
       <c r="W165" t="inlineStr">
         <is>
-          <t>MACアドレスフィルタリング,ANY接続拒否,無線LAN,SSID</t>
+          <t>MACアドレスフィルタリング|MACアドレスフィルタリング 工事担任者</t>
         </is>
       </c>
     </row>
@@ -16431,7 +16431,7 @@
       </c>
       <c r="W166" t="inlineStr">
         <is>
-          <t>IPsec,トランスポートモード,トンネルモード,VPN</t>
+          <t>IPsec|IPsec 工事担任者</t>
         </is>
       </c>
     </row>
@@ -16529,7 +16529,7 @@
       </c>
       <c r="W167" t="inlineStr">
         <is>
-          <t>アンチパスバック,入退室管理,セキュリティ</t>
+          <t>アンチパスバック|アンチパスバック 工事担任者</t>
         </is>
       </c>
     </row>
@@ -16624,7 +16624,7 @@
       </c>
       <c r="W168" t="inlineStr">
         <is>
-          <t>光導通試験,SI形,GI形,励振,PINホトダイオード</t>
+          <t>光導通試験|光導通試験 工事担任者</t>
         </is>
       </c>
     </row>
@@ -16724,7 +16724,7 @@
       </c>
       <c r="W169" t="inlineStr">
         <is>
-          <t>POF,フッ素樹脂,アクリル樹脂,プラスチック光ファイバ</t>
+          <t>POF|POF プラスチック光ファイバ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -16827,7 +16827,7 @@
       </c>
       <c r="W170" t="inlineStr">
         <is>
-          <t>1000BASE-T,UTP,8心,カテゴリ5e,全二重</t>
+          <t>1000BASE-T|1000BASE-T 工事担任者,1000BASE-TX|1000BASE-TX 工事担任者</t>
         </is>
       </c>
     </row>
@@ -16923,7 +16923,7 @@
       </c>
       <c r="W171" t="inlineStr">
         <is>
-          <t>反射減衰量,挿入損失,UTPケーブル,JIS X 5150</t>
+          <t>反射減衰量|反射減衰量 工事担任者</t>
         </is>
       </c>
     </row>
@@ -17021,7 +17021,7 @@
       </c>
       <c r="W172" t="inlineStr">
         <is>
-          <t>クロスコネクト,クラスE,水平ケーブル,JIS X 5150</t>
+          <t>JIS X 5150|JIS X 5150 工事担任者</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="W173" t="inlineStr">
         <is>
-          <t>FASコネクタ,ターミネーションコネクタ,SC型,光キャビネット</t>
+          <t>FASコネクタ|FASコネクタ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -17207,7 +17207,7 @@
       </c>
       <c r="W174" t="inlineStr">
         <is>
-          <t>反射減衰量,挿入損失,クラスC,JIS X 5150</t>
+          <t>JIS X 5150|JIS X 5150 反射減衰量 工事担任者</t>
         </is>
       </c>
     </row>
@@ -17300,7 +17300,7 @@
       </c>
       <c r="W175" t="inlineStr">
         <is>
-          <t>融着接続,気泡,光ファイバカッタ,端面切断</t>
+          <t>融着接続|融着接続 気泡 工事担任者</t>
         </is>
       </c>
     </row>
@@ -17401,7 +17401,7 @@
       </c>
       <c r="W176" t="inlineStr">
         <is>
-          <t>設計図書,不整合,発注者,受注者,施工管理</t>
+          <t>設計図書|設計図書 不整合 工事担任者</t>
         </is>
       </c>
     </row>
@@ -17504,7 +17504,7 @@
       </c>
       <c r="W177" t="inlineStr">
         <is>
-          <t>アローダイアグラム,クリティカルパス,フリーフロート,PERT</t>
+          <t>アローダイアグラム|アローダイアグラム 工事担任者,フリーフロート|フリーフロート 工事担任者</t>
         </is>
       </c>
     </row>
@@ -17594,7 +17594,7 @@
       </c>
       <c r="W178" t="inlineStr">
         <is>
-          <t>重要通信,相互接続,電気通信事業法</t>
+          <t>重要通信|重要通信 相互接続 工事担任者</t>
         </is>
       </c>
     </row>
@@ -17688,7 +17688,7 @@
       </c>
       <c r="W179" t="inlineStr">
         <is>
-          <t>重要通信,緊急通信,天災,選挙管理機関</t>
+          <t>重要通信|重要通信 緊急通信 工事担任者</t>
         </is>
       </c>
     </row>
@@ -17785,7 +17785,7 @@
       </c>
       <c r="W180" t="inlineStr">
         <is>
-          <t>業務改善命令,重要通信,適切に配慮,電気通信事業法</t>
+          <t>業務改善命令|業務改善命令 重要通信 工事担任者</t>
         </is>
       </c>
     </row>
@@ -17882,7 +17882,7 @@
       </c>
       <c r="W181" t="inlineStr">
         <is>
-          <t>管理規程,確実かつ安定的,電気通信事業法</t>
+          <t>管理規程|管理規程 確実かつ安定的 工事担任者</t>
         </is>
       </c>
     </row>
@@ -17974,7 +17974,7 @@
       </c>
       <c r="W182" t="inlineStr">
         <is>
-          <t>端末設備,接続請求,電波,電気通信事業法</t>
+          <t>端末設備|端末設備 接続請求 工事担任者</t>
         </is>
       </c>
     </row>
@@ -18074,7 +18074,7 @@
       </c>
       <c r="W183" t="inlineStr">
         <is>
-          <t>工事担任者,第一級デジタル通信,総合デジタル通信用設備,資格区分</t>
+          <t>第一級デジタル通信|第一級デジタル通信 工事担任者</t>
         </is>
       </c>
     </row>
@@ -18173,7 +18173,7 @@
       </c>
       <c r="W184" t="inlineStr">
         <is>
-          <t>資格者証,書換え交付,再交付,住所変更</t>
+          <t>資格者証|資格者証 書換え交付 工事担任者</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="W185" t="inlineStr">
         <is>
-          <t>技術基準適合認定番号,デジタルデータ伝送用設備,認定番号</t>
+          <t>技術基準適合認定番号|技術基準適合認定番号 工事担任者</t>
         </is>
       </c>
     </row>
@@ -18372,7 +18372,7 @@
       </c>
       <c r="W186" t="inlineStr">
         <is>
-          <t>有線電気通信法,設置及び使用,秩序,公共の福祉</t>
+          <t>有線電気通信法|有線電気通信法 目的 工事担任者</t>
         </is>
       </c>
     </row>
@@ -18469,7 +18469,7 @@
       </c>
       <c r="W187" t="inlineStr">
         <is>
-          <t>非常事態,有線電気通信法,通信確保,命令</t>
+          <t>有線電気通信法|有線電気通信法 非常事態 工事担任者</t>
         </is>
       </c>
     </row>
@@ -18569,7 +18569,7 @@
       </c>
       <c r="W188" t="inlineStr">
         <is>
-          <t>専用通信回線設備等端末,通話チャネル,制御チャネル,端末設備等規則</t>
+          <t>専用通信回線設備等端末|専用通信回線設備等端末 工事担任者,通話チャネル|通話チャネル 工事担任者</t>
         </is>
       </c>
     </row>
@@ -18663,7 +18663,7 @@
       </c>
       <c r="W189" t="inlineStr">
         <is>
-          <t>分界点,鳴音,事業用電気通信設備,端末設備等規則</t>
+          <t>分界点|分界点 鳴音 工事担任者</t>
         </is>
       </c>
     </row>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="W190" t="inlineStr">
         <is>
-          <t>事業用電気通信設備,識別機能,漏えい,端末設備等規則</t>
+          <t>識別機能|識別機能 事業用電気通信設備 工事担任者</t>
         </is>
       </c>
     </row>
@@ -18857,7 +18857,7 @@
       </c>
       <c r="W191" t="inlineStr">
         <is>
-          <t>評価雑音電力,実効的雑音電力,マイナス64dB,端末設備等規則</t>
+          <t>評価雑音電力|評価雑音電力 工事担任者</t>
         </is>
       </c>
     </row>
@@ -18946,7 +18946,7 @@
       </c>
       <c r="W192" t="inlineStr">
         <is>
-          <t>配線設備,強電流電線,有線電気通信設備令,告示</t>
+          <t>配線設備|配線設備 強電流電線 工事担任者</t>
         </is>
       </c>
     </row>
@@ -19046,7 +19046,7 @@
       </c>
       <c r="W193" t="inlineStr">
         <is>
-          <t>押しボタンダイヤル,ダイヤル番号,16種類,ミニマムポーズ</t>
+          <t>ダイヤル番号|ダイヤル番号 16種類 工事担任者,ミニマムポーズ|ミニマムポーズ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -19143,7 +19143,7 @@
       </c>
       <c r="W194" t="inlineStr">
         <is>
-          <t>IP移動電話端末,128秒,通信終了メッセージ,応答確認</t>
+          <t>IP移動電話端末|IP移動電話端末 128秒 工事担任者</t>
         </is>
       </c>
     </row>
@@ -19240,7 +19240,7 @@
       </c>
       <c r="W195" t="inlineStr">
         <is>
-          <t>専用通信回線設備等端末,漏話減衰量,1500Hz,70dB</t>
+          <t>漏話減衰量|漏話減衰量 1500Hz 工事担任者</t>
         </is>
       </c>
     </row>
@@ -19334,7 +19334,7 @@
       </c>
       <c r="W196" t="inlineStr">
         <is>
-          <t>専用通信回線設備等端末,直流電圧,電気的条件,光学的条件</t>
+          <t>専用通信回線設備等端末|専用通信回線設備等端末 直流電圧 工事担任者</t>
         </is>
       </c>
     </row>
@@ -19434,7 +19434,7 @@
       </c>
       <c r="W197" t="inlineStr">
         <is>
-          <t>初期識別符号,変更を促す機能,アクセス制御,端末設備等規則</t>
+          <t>初期識別符号|初期識別符号 工事担任者</t>
         </is>
       </c>
     </row>
@@ -19539,7 +19539,7 @@
       </c>
       <c r="W198" t="inlineStr">
         <is>
-          <t>音声周波,高周波,離隔距離,有線電気通信法</t>
+          <t>音声周波|音声周波 高周波 工事担任者</t>
         </is>
       </c>
     </row>
@@ -19633,7 +19633,7 @@
       </c>
       <c r="W199" t="inlineStr">
         <is>
-          <t>足場金具,1.8メートル,架空電線,有線電気通信設備令</t>
+          <t>足場金具|足場金具 1.8メートル 工事担任者</t>
         </is>
       </c>
     </row>
@@ -19735,7 +19735,7 @@
       </c>
       <c r="W200" t="inlineStr">
         <is>
-          <t>架空電線,支持物,強電流電線,1メートル,有線電気通信設備令</t>
+          <t>架空電線|架空電線 支持物 離隔距離 工事担任者</t>
         </is>
       </c>
     </row>
@@ -19829,7 +19829,7 @@
       </c>
       <c r="W201" t="inlineStr">
         <is>
-          <t>アクセス管理者,動作を管理する者,不正アクセス禁止法</t>
+          <t>アクセス管理者|アクセス管理者 工事担任者</t>
         </is>
       </c>
     </row>
@@ -19926,7 +19926,7 @@
       </c>
       <c r="W202" t="inlineStr">
         <is>
-          <t>電子署名法,流通及び情報処理,公共の福祉</t>
+          <t>電子署名法|電子署名法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -20019,7 +20019,7 @@
       </c>
       <c r="W203" t="inlineStr">
         <is>
-          <t>GE-PON,OLT,TDMA,P2MPディスカバリ,DBA</t>
+          <t>GE-PON|GE-PON 工事担任者,DBA|DBA 動的帯域割当 工事担任者</t>
         </is>
       </c>
     </row>
@@ -20114,7 +20114,7 @@
       </c>
       <c r="W204" t="inlineStr">
         <is>
-          <t>クラウド型PBX,SIP,アプリケーション層,IP電話</t>
+          <t>クラウド型PBX|クラウド型PBX 工事担任者,SIP|SIP アプリケーション層 工事担任者</t>
         </is>
       </c>
     </row>
@@ -20207,7 +20207,7 @@
       </c>
       <c r="W205" t="inlineStr">
         <is>
-          <t>PoE,IEEE802.3at,Type1,Class0,350mA</t>
+          <t>IEEE802.3at|IEEE802.3at Type1 工事担任者</t>
         </is>
       </c>
     </row>
@@ -20305,7 +20305,7 @@
       </c>
       <c r="W206" t="inlineStr">
         <is>
-          <t>IEEE802.11n,IEEE802.11ax,Wi-Fi 6,2.4GHz,5GHz</t>
+          <t>IEEE802.11n|IEEE802.11n 工事担任者,IEEE802.11ax|IEEE802.11ax Wi-Fi6 工事担任者</t>
         </is>
       </c>
     </row>
@@ -20403,7 +20403,7 @@
       </c>
       <c r="W207" t="inlineStr">
         <is>
-          <t>コモンモードノイズ,ノーマルモードノイズ,誘導雑音,EMC</t>
+          <t>コモンモードノイズ|コモンモードノイズ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -20496,7 +20496,7 @@
       </c>
       <c r="W208" t="inlineStr">
         <is>
-          <t>10GBASE-LR,64B/66B,8B/10B,8B1Q4,符号化</t>
+          <t>10GBASE-LR|10GBASE-LR 工事担任者,64B/66B|64B/66B 工事担任者</t>
         </is>
       </c>
     </row>
@@ -20589,7 +20589,7 @@
       </c>
       <c r="W209" t="inlineStr">
         <is>
-          <t>FM一括変換方式,CATV,光強度変調,3GHz</t>
+          <t>FM一括変換方式|FM一括変換方式 工事担任者</t>
         </is>
       </c>
     </row>
@@ -20687,7 +20687,7 @@
       </c>
       <c r="W210" t="inlineStr">
         <is>
-          <t>10GBASE-SR,850nm,マルチモード光ファイバ,10GBASE-LR</t>
+          <t>10GBASE-SR|10GBASE-SR 工事担任者</t>
         </is>
       </c>
     </row>
@@ -20787,7 +20787,7 @@
       </c>
       <c r="W211" t="inlineStr">
         <is>
-          <t>ICMPv6,IPv6,パケット分割,PMTUD</t>
+          <t>ICMPv6|ICMPv6 工事担任者</t>
         </is>
       </c>
     </row>
@@ -20880,7 +20880,7 @@
       </c>
       <c r="W212" t="inlineStr">
         <is>
-          <t>EoMPLS,LER,MPLS,L2ヘッダ,プリアンブル</t>
+          <t>EoMPLS|EoMPLS 工事担任者,LER|LER MPLS 工事担任者,MPLS|MPLS 工事担任者</t>
         </is>
       </c>
     </row>
@@ -20980,7 +20980,7 @@
       </c>
       <c r="W213" t="inlineStr">
         <is>
-          <t>バックドア,フィッシング,ボット,スキミング,マルウェア</t>
+          <t>バックドア|バックドア 工事担任者,フィッシング|フィッシング 工事担任者</t>
         </is>
       </c>
     </row>
@@ -21073,7 +21073,7 @@
       </c>
       <c r="W214" t="inlineStr">
         <is>
-          <t>IPsec,トンネルモード,トランスポートモード,VPN,PPP</t>
+          <t>IPsec|IPsec 工事担任者</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="W215" t="inlineStr">
         <is>
-          <t>パケットフィルタリング,ポートスキャン,ファイアウォール</t>
+          <t>パケットフィルタリング|パケットフィルタリング ポートスキャン 工事担任者</t>
         </is>
       </c>
     </row>
@@ -21272,7 +21272,7 @@
       </c>
       <c r="W216" t="inlineStr">
         <is>
-          <t>IPS,IDS,不正アクセス検知,自動遮断</t>
+          <t>IPS|IPS IDS 工事担任者</t>
         </is>
       </c>
     </row>
@@ -21372,7 +21372,7 @@
       </c>
       <c r="W217" t="inlineStr">
         <is>
-          <t>アンチパスバック,ゾーニング,入退室管理,セキュリティ</t>
+          <t>アンチパスバック|アンチパスバック 工事担任者,ゾーニング|ゾーニング 工事担任者</t>
         </is>
       </c>
     </row>
@@ -21473,7 +21473,7 @@
       </c>
       <c r="W218" t="inlineStr">
         <is>
-          <t>融着接続,スクリーニング試験,引張試験,光ファイバ</t>
+          <t>融着接続|融着接続 スクリーニング試験 工事担任者</t>
         </is>
       </c>
     </row>
@@ -21573,7 +21573,7 @@
       </c>
       <c r="W219" t="inlineStr">
         <is>
-          <t>1000BASE-TX,1000BASE-T,カテゴリ6,カテゴリ5e,UTP</t>
+          <t>1000BASE-TX|1000BASE-TX 工事担任者,1000BASE-T|1000BASE-T 工事担任者</t>
         </is>
       </c>
     </row>
@@ -21666,7 +21666,7 @@
       </c>
       <c r="W220" t="inlineStr">
         <is>
-          <t>交差接続,クロスコネクト,光配線盤,ジャンパコード</t>
+          <t>交差接続|交差接続 クロスコネクト 工事担任者</t>
         </is>
       </c>
     </row>
@@ -21759,7 +21759,7 @@
       </c>
       <c r="W221" t="inlineStr">
         <is>
-          <t>T568B,RJ-45,心線配色,UTPケーブル</t>
+          <t>T568B|T568B 工事担任者</t>
         </is>
       </c>
     </row>
@@ -21857,7 +21857,7 @@
       </c>
       <c r="W222" t="inlineStr">
         <is>
-          <t>インタコネクト,クラスE,水平ケーブル,81.5m,JIS X 5150</t>
+          <t>JIS X 5150|JIS X 5150 インタコネクト 工事担任者</t>
         </is>
       </c>
     </row>
@@ -21954,7 +21954,7 @@
       </c>
       <c r="W223" t="inlineStr">
         <is>
-          <t>光キャビネット,光ローゼット,ドロップ光ファイバ,インドア光ファイバ</t>
+          <t>光キャビネット|光キャビネット 光ローゼット 工事担任者</t>
         </is>
       </c>
     </row>
@@ -22046,7 +22046,7 @@
       </c>
       <c r="W224" t="inlineStr">
         <is>
-          <t>STP,IEEE802.1D,スパニングツリー,ループ防止</t>
+          <t>STP|STP IEEE802.1D 工事担任者</t>
         </is>
       </c>
     </row>
@@ -22138,7 +22138,7 @@
       </c>
       <c r="W225" t="inlineStr">
         <is>
-          <t>OTDR,ダイナミックレンジ,後方散乱光,パルスパワー</t>
+          <t>OTDRダイナミックレンジ|OTDR ダイナミックレンジ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -22237,7 +22237,7 @@
       </c>
       <c r="W226" t="inlineStr">
         <is>
-          <t>施工計画書,現場代理人,監督員,受注者,発注者</t>
+          <t>施工計画書|施工計画書 工事担任者</t>
         </is>
       </c>
     </row>
@@ -22334,7 +22334,7 @@
       </c>
       <c r="W227" t="inlineStr">
         <is>
-          <t>アローダイアグラム,クリティカルパス,トータルフロート,PERT</t>
+          <t>クリティカルパス|クリティカルパス 工事担任者,トータルフロート|トータルフロート 工事担任者</t>
         </is>
       </c>
     </row>
@@ -22435,7 +22435,7 @@
       </c>
       <c r="W228" t="inlineStr">
         <is>
-          <t>資格者証,工事担任者,罰金,5年,養成課程</t>
+          <t>資格者証|資格者証 罰金 5年 工事担任者</t>
         </is>
       </c>
     </row>
@@ -22535,7 +22535,7 @@
       </c>
       <c r="W229" t="inlineStr">
         <is>
-          <t>管理規程,事業開始前,届出,技術基準,電気通信事業法</t>
+          <t>管理規程|管理規程 事業開始前 届出 工事担任者</t>
         </is>
       </c>
     </row>
@@ -22628,7 +22628,7 @@
       </c>
       <c r="W230" t="inlineStr">
         <is>
-          <t>自営電気通信設備,保持,経営上困難,接続拒否,総務大臣</t>
+          <t>自営電気通信設備|自営電気通信設備 保持 工事担任者</t>
         </is>
       </c>
     </row>
@@ -22718,7 +22718,7 @@
       </c>
       <c r="W231" t="inlineStr">
         <is>
-          <t>技術基準適合認定,表示,総務大臣,公示</t>
+          <t>技術基準適合認定|技術基準適合認定 工事担任者</t>
         </is>
       </c>
     </row>
@@ -22811,7 +22811,7 @@
       </c>
       <c r="W232" t="inlineStr">
         <is>
-          <t>重要通信,公共の利益,緊急通信,人命の安全</t>
+          <t>重要通信|重要通信 人命安全 工事担任者</t>
         </is>
       </c>
     </row>
@@ -22911,7 +22911,7 @@
       </c>
       <c r="W233" t="inlineStr">
         <is>
-          <t>工事担任者,第一級アナログ通信,アナログ伝送路設備,総合デジタル通信用設備</t>
+          <t>第一級アナログ通信|第一級アナログ通信 工事担任者</t>
         </is>
       </c>
     </row>
@@ -23010,7 +23010,7 @@
       </c>
       <c r="W234" t="inlineStr">
         <is>
-          <t>資格者証,再交付,失った,技術の向上,端末設備等</t>
+          <t>資格者証|資格者証 再交付 工事担任者</t>
         </is>
       </c>
     </row>
@@ -23110,7 +23110,7 @@
       </c>
       <c r="W235" t="inlineStr">
         <is>
-          <t>技術基準適合認定番号,IP電話用設備,E,認定番号</t>
+          <t>技術基準適合認定番号|技術基準適合認定番号 工事担任者</t>
         </is>
       </c>
     </row>
@@ -23202,7 +23202,7 @@
       </c>
       <c r="W236" t="inlineStr">
         <is>
-          <t>有線電気通信法,設置及び使用,秩序,公共の福祉</t>
+          <t>有線電気通信法|有線電気通信法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -23294,7 +23294,7 @@
       </c>
       <c r="W237" t="inlineStr">
         <is>
-          <t>非常事態,有線電気通信法,通信確保,使用させ,接続</t>
+          <t>有線電気通信法|有線電気通信法 非常事態 工事担任者</t>
         </is>
       </c>
     </row>
@@ -23399,7 +23399,7 @@
       </c>
       <c r="W238" t="inlineStr">
         <is>
-          <t>専用通信回線設備等端末,デジタルデータ伝送用設備,端末設備等規則</t>
+          <t>専用通信回線設備等端末|専用通信回線設備等端末 工事担任者</t>
         </is>
       </c>
     </row>
@@ -23491,7 +23491,7 @@
       </c>
       <c r="W239" t="inlineStr">
         <is>
-          <t>直流回路,アナログ電話用設備,交換設備,端末設備等規則</t>
+          <t>直流回路|直流回路 アナログ電話用設備 工事担任者</t>
         </is>
       </c>
     </row>
@@ -23590,7 +23590,7 @@
       </c>
       <c r="W240" t="inlineStr">
         <is>
-          <t>分界点,事業用電気通信設備,端末設備,接続方式</t>
+          <t>分界点|分界点 事業用電気通信設備 工事担任者</t>
         </is>
       </c>
     </row>
@@ -23687,7 +23687,7 @@
       </c>
       <c r="W241" t="inlineStr">
         <is>
-          <t>絶縁抵抗,使用電圧,300V,0.2MΩ,端末設備等規則</t>
+          <t>絶縁抵抗|絶縁抵抗 300V以下 工事担任者</t>
         </is>
       </c>
     </row>
@@ -23786,7 +23786,7 @@
       </c>
       <c r="W242" t="inlineStr">
         <is>
-          <t>配線設備,絶縁抵抗,直流200V,1MΩ,告示</t>
+          <t>配線設備|配線設備 絶縁抵抗 直流200V 工事担任者</t>
         </is>
       </c>
     </row>
@@ -23891,7 +23891,7 @@
       </c>
       <c r="W243" t="inlineStr">
         <is>
-          <t>ミニマムポーズ,押しボタンダイヤル,高群周波数,信号周波数偏差</t>
+          <t>ミニマムポーズ|ミニマムポーズ 工事担任者,押しボタンダイヤル信号|押しボタンダイヤル信号 工事担任者</t>
         </is>
       </c>
     </row>
@@ -23983,7 +23983,7 @@
       </c>
       <c r="W244" t="inlineStr">
         <is>
-          <t>アナログ電話端末,緊急通報,警察機関,海上保安,消防機関</t>
+          <t>緊急通報|緊急通報 アナログ電話端末 工事担任者</t>
         </is>
       </c>
     </row>
@@ -24088,7 +24088,7 @@
       </c>
       <c r="W245" t="inlineStr">
         <is>
-          <t>IP電話端末,自動再発信,3分間,2回以内</t>
+          <t>自動再発信|自動再発信 IP電話端末 工事担任者</t>
         </is>
       </c>
     </row>
@@ -24180,7 +24180,7 @@
       </c>
       <c r="W246" t="inlineStr">
         <is>
-          <t>移動電話端末,漏話減衰量,1500Hz,70dB</t>
+          <t>漏話減衰量|漏話減衰量 移動電話端末 工事担任者</t>
         </is>
       </c>
     </row>
@@ -24269,7 +24269,7 @@
       </c>
       <c r="W247" t="inlineStr">
         <is>
-          <t>専用通信回線設備等端末,ソフトウェア更新,アクセス制御,電力停止</t>
+          <t>アクセス制御|アクセス制御 ソフトウェア更新 工事担任者</t>
         </is>
       </c>
     </row>
@@ -24363,7 +24363,7 @@
       </c>
       <c r="W248" t="inlineStr">
         <is>
-          <t>有線電気通信設備,絶縁機能,避雷機能,保安機能</t>
+          <t>保安機能|保安機能 有線電気通信設備 工事担任者</t>
         </is>
       </c>
     </row>
@@ -24468,7 +24468,7 @@
       </c>
       <c r="W249" t="inlineStr">
         <is>
-          <t>電線,強電流電線,重畳,有線電気通信法</t>
+          <t>電線|電線 強電流電線 工事担任者</t>
         </is>
       </c>
     </row>
@@ -24557,7 +24557,7 @@
       </c>
       <c r="W250" t="inlineStr">
         <is>
-          <t>屋内電線,高圧,強電流ケーブル,離隔距離,隔壁</t>
+          <t>屋内電線|屋内電線 強電流ケーブル 工事担任者</t>
         </is>
       </c>
     </row>
@@ -24649,7 +24649,7 @@
       </c>
       <c r="W251" t="inlineStr">
         <is>
-          <t>アクセス管理者,アクセス制御機能,有効性,高度化,不正アクセス禁止法</t>
+          <t>不正アクセス禁止法|不正アクセス禁止法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -24741,7 +24741,7 @@
       </c>
       <c r="W252" t="inlineStr">
         <is>
-          <t>電子署名法,真正に成立,推定,電磁的記録</t>
+          <t>電子署名法|電子署名法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -24829,7 +24829,7 @@
       </c>
       <c r="W253" t="inlineStr">
         <is>
-          <t>10G-EPON,GE-PON,デュアルレートバースト受信器,OLT</t>
+          <t>デュアルレートバースト受信器|デュアルレートバースト受信器 工事担任者</t>
         </is>
       </c>
     </row>
@@ -24929,7 +24929,7 @@
       </c>
       <c r="W254" t="inlineStr">
         <is>
-          <t>IPセントレックス,IP-PBX,ハードウェアタイプ,ソフトウェアタイプ</t>
+          <t>IPセントレックス|IPセントレックス 工事担任者,IP-PBX|IP-PBX 工事担任者</t>
         </is>
       </c>
     </row>
@@ -25022,7 +25022,7 @@
       </c>
       <c r="W255" t="inlineStr">
         <is>
-          <t>IEEE802.11ax,Wi-Fi 6,6GHz,ISMバンド,気象レーダ</t>
+          <t>IEEE802.11ax|IEEE802.11ax 6GHz 工事担任者</t>
         </is>
       </c>
     </row>
@@ -25115,7 +25115,7 @@
       </c>
       <c r="W256" t="inlineStr">
         <is>
-          <t>IEEE802.3bt,Type4,Class8,90W,PoE</t>
+          <t>IEEE802.3bt|IEEE802.3bt Type4 工事担任者</t>
         </is>
       </c>
     </row>
@@ -25208,7 +25208,7 @@
       </c>
       <c r="W257" t="inlineStr">
         <is>
-          <t>誘導雷サージ,電磁誘導,静電誘導,過電圧,雷保護</t>
+          <t>誘導雷サージ|誘導雷サージ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -25301,7 +25301,7 @@
       </c>
       <c r="W258" t="inlineStr">
         <is>
-          <t>4D-PAM5,1000BASE-T,PAM,5値,符号化</t>
+          <t>4D-PAM5|4D-PAM5 1000BASE-T 工事担任者</t>
         </is>
       </c>
     </row>
@@ -25399,7 +25399,7 @@
       </c>
       <c r="W259" t="inlineStr">
         <is>
-          <t>CWDM,DWDM,波長多重,20nm,アクセス系</t>
+          <t>CWDM|CWDM 工事担任者,DWDM|DWDM 工事担任者</t>
         </is>
       </c>
     </row>
@@ -25492,7 +25492,7 @@
       </c>
       <c r="W260" t="inlineStr">
         <is>
-          <t>SDN,NFV,データプレーン,コントロールプレーン</t>
+          <t>SDN|SDN 工事担任者,NFV|NFV 工事担任者</t>
         </is>
       </c>
     </row>
@@ -25585,7 +25585,7 @@
       </c>
       <c r="W261" t="inlineStr">
         <is>
-          <t>トンネリング,デュアルスタック,IPv4,IPv6,カプセル化</t>
+          <t>トンネリング|トンネリング IPv6 工事担任者</t>
         </is>
       </c>
     </row>
@@ -25685,7 +25685,7 @@
       </c>
       <c r="W262" t="inlineStr">
         <is>
-          <t>EoMPLS,LER,LSR,MPLS,ラベルスイッチング</t>
+          <t>EoMPLS|EoMPLS 工事担任者,LER|LER 工事担任者,LSR|LSR MPLS 工事担任者</t>
         </is>
       </c>
     </row>
@@ -25778,7 +25778,7 @@
       </c>
       <c r="W263" t="inlineStr">
         <is>
-          <t>OP25B,SPF,DKIM,迷惑メール対策,25番ポート</t>
+          <t>OP25B|OP25B 工事担任者,DKIM|DKIM 工事担任者</t>
         </is>
       </c>
     </row>
@@ -25878,7 +25878,7 @@
       </c>
       <c r="W264" t="inlineStr">
         <is>
-          <t>デジタル署名,公開鍵暗号,送信否認防止,メッセージ認証</t>
+          <t>デジタル署名|デジタル署名 否認防止 工事担任者</t>
         </is>
       </c>
     </row>
@@ -25978,7 +25978,7 @@
       </c>
       <c r="W265" t="inlineStr">
         <is>
-          <t>チェックサム,ウイルス,改変検出,メールサーバ</t>
+          <t>チェックサム|チェックサム ウイルス 工事担任者</t>
         </is>
       </c>
     </row>
@@ -26069,7 +26069,7 @@
       </c>
       <c r="W266" t="inlineStr">
         <is>
-          <t>サニタイジング,XSS,クロスサイトスクリプティング,HTMLタグ</t>
+          <t>サニタイジング|サニタイジング 工事担任者</t>
         </is>
       </c>
     </row>
@@ -26162,7 +26162,7 @@
       </c>
       <c r="W267" t="inlineStr">
         <is>
-          <t>ベースラインアプローチ,詳細リスク分析,リスク分析手法,ISMS</t>
+          <t>ベースラインアプローチ|ベースラインアプローチ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -26257,7 +26257,7 @@
       </c>
       <c r="W268" t="inlineStr">
         <is>
-          <t>光導通試験,SI形,GI形,励振,コア径</t>
+          <t>光導通試験|光導通試験 SI形 GI形 工事担任者,PINホトダイオード|PINホトダイオード 工事担任者</t>
         </is>
       </c>
     </row>
@@ -26355,7 +26355,7 @@
       </c>
       <c r="W269" t="inlineStr">
         <is>
-          <t>PoE,オルタナティブA,オルタナティブB,ピン4・5・7・8</t>
+          <t>PoEオルタナティブB|PoE オルタナティブB 工事担任者</t>
         </is>
       </c>
     </row>
@@ -26448,7 +26448,7 @@
       </c>
       <c r="W270" t="inlineStr">
         <is>
-          <t>光ファイバケーブル,けん引速度,20メートル,OITDA</t>
+          <t>けん引速度|光ファイバ けん引速度 工事担任者</t>
         </is>
       </c>
     </row>
@@ -26541,7 +26541,7 @@
       </c>
       <c r="W271" t="inlineStr">
         <is>
-          <t>プライベートIPアドレス,クラスB,172.16,IPv4</t>
+          <t>プライベートIPアドレス|プライベートIPアドレス クラスB 工事担任者</t>
         </is>
       </c>
     </row>
@@ -26639,7 +26639,7 @@
       </c>
       <c r="W272" t="inlineStr">
         <is>
-          <t>クロスコネクト,クラスF,水平ケーブル,JIS X 5150</t>
+          <t>JIS X 5150|JIS X 5150 クラスF 工事担任者</t>
         </is>
       </c>
     </row>
@@ -26732,7 +26732,7 @@
       </c>
       <c r="W273" t="inlineStr">
         <is>
-          <t>CSMA/CD,全二重,半二重,オートネゴシエーション,衝突</t>
+          <t>CSMA/CD|CSMA/CD 工事担任者,全二重通信|全二重通信 CSMA/CD 工事担任者</t>
         </is>
       </c>
     </row>
@@ -26825,7 +26825,7 @@
       </c>
       <c r="W274" t="inlineStr">
         <is>
-          <t>MPOコネクタ,多心光コネクタ,プッシュプル,12心,24心</t>
+          <t>MPOコネクタ|MPOコネクタ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -26918,7 +26918,7 @@
       </c>
       <c r="W275" t="inlineStr">
         <is>
-          <t>細径インドア光ケーブル,低摩擦,集合住宅,押し込み工法</t>
+          <t>細径インドア光ケーブル|細径インドア光ケーブル 工事担任者</t>
         </is>
       </c>
     </row>
@@ -27024,7 +27024,7 @@
       </c>
       <c r="W276" t="inlineStr">
         <is>
-          <t>KY活動,危険予知,ほう・れん・そう,安全管理</t>
+          <t>KY活動|KY活動 危険予知 工事担任者</t>
         </is>
       </c>
     </row>
@@ -27125,7 +27125,7 @@
       </c>
       <c r="W277" t="inlineStr">
         <is>
-          <t>アローダイアグラム,クリティカルパス,トータルフロート,PERT</t>
+          <t>クリティカルパス|クリティカルパス 工事担任者</t>
         </is>
       </c>
     </row>
@@ -27226,7 +27226,7 @@
       </c>
       <c r="W278" t="inlineStr">
         <is>
-          <t>技術基準,責任の分界,設置の場所,電気通信事業法</t>
+          <t>技術基準|技術基準 責任の分界 工事担任者</t>
         </is>
       </c>
     </row>
@@ -27314,7 +27314,7 @@
       </c>
       <c r="W279" t="inlineStr">
         <is>
-          <t>業務改善命令,修理,支障,電気通信事業法</t>
+          <t>業務改善命令|業務改善命令 工事担任者</t>
         </is>
       </c>
     </row>
@@ -27407,7 +27407,7 @@
       </c>
       <c r="W280" t="inlineStr">
         <is>
-          <t>技術基準,修理,改造,使用制限,総務大臣</t>
+          <t>技術基準|技術基準 修理 改造 工事担任者</t>
         </is>
       </c>
     </row>
@@ -27500,7 +27500,7 @@
       </c>
       <c r="W281" t="inlineStr">
         <is>
-          <t>端末設備,接続請求,電波,電気通信事業法</t>
+          <t>端末設備|端末設備 接続請求 電波 工事担任者</t>
         </is>
       </c>
     </row>
@@ -27595,7 +27595,7 @@
       </c>
       <c r="W282" t="inlineStr">
         <is>
-          <t>重要通信,気象,水象,生活基盤,緊急通信</t>
+          <t>重要通信|重要通信 生活基盤 工事担任者</t>
         </is>
       </c>
     </row>
@@ -27685,7 +27685,7 @@
       </c>
       <c r="W283" t="inlineStr">
         <is>
-          <t>工事担任者,第二級デジタル通信,1Gbps,第一級アナログ,資格区分</t>
+          <t>第二級デジタル通信|第二級デジタル通信 工事担任者</t>
         </is>
       </c>
     </row>
@@ -27784,7 +27784,7 @@
       </c>
       <c r="W284" t="inlineStr">
         <is>
-          <t>資格者証,書換え交付,返納,10日以内</t>
+          <t>資格者証|資格者証 書換え交付 返納 工事担任者</t>
         </is>
       </c>
     </row>
@@ -27889,7 +27889,7 @@
       </c>
       <c r="W285" t="inlineStr">
         <is>
-          <t>技術基準適合認定番号,総合デジタル通信用設備,C,認定番号</t>
+          <t>技術基準適合認定番号|技術基準適合認定番号 工事担任者</t>
         </is>
       </c>
     </row>
@@ -27994,7 +27994,7 @@
       </c>
       <c r="W286" t="inlineStr">
         <is>
-          <t>有線電気通信法,設置及び使用,秩序,公共の福祉</t>
+          <t>有線電気通信法|有線電気通信法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -28086,7 +28086,7 @@
       </c>
       <c r="W287" t="inlineStr">
         <is>
-          <t>有線電気通信設備,本邦外,総務大臣,許可</t>
+          <t>有線電気通信設備令|有線電気通信設備令 本邦外 工事担任者</t>
         </is>
       </c>
     </row>
@@ -28192,7 +28192,7 @@
       </c>
       <c r="W288" t="inlineStr">
         <is>
-          <t>IP電話端末,IP電話用設備,デジタルデータ伝送用設備,端末設備等規則</t>
+          <t>IP電話端末|IP電話端末 工事担任者</t>
         </is>
       </c>
     </row>
@@ -28292,7 +28292,7 @@
       </c>
       <c r="W289" t="inlineStr">
         <is>
-          <t>端末設備,事業用電気通信設備,識別機能,鳴音</t>
+          <t>識別機能|識別機能 鳴音 工事担任者</t>
         </is>
       </c>
     </row>
@@ -28392,7 +28392,7 @@
       </c>
       <c r="W290" t="inlineStr">
         <is>
-          <t>接地抵抗,100オーム,絶縁耐力,端末設備等規則</t>
+          <t>接地抵抗|接地抵抗 100オーム 工事担任者</t>
         </is>
       </c>
     </row>
@@ -28490,7 +28490,7 @@
       </c>
       <c r="W291" t="inlineStr">
         <is>
-          <t>評価雑音電力,マイナス64dB,マイナス58dB,端末設備等規則</t>
+          <t>評価雑音電力|評価雑音電力 工事担任者</t>
         </is>
       </c>
     </row>
@@ -28591,7 +28591,7 @@
       </c>
       <c r="W292" t="inlineStr">
         <is>
-          <t>識別符号,無線設備,交換設備,端末設備等規則</t>
+          <t>識別符号|識別符号 無線設備 工事担任者</t>
         </is>
       </c>
     </row>
@@ -28690,7 +28690,7 @@
       </c>
       <c r="W293" t="inlineStr">
         <is>
-          <t>信号周波数偏差,±1.5%,ミニマムポーズ,周期,押しボタンダイヤル</t>
+          <t>信号周波数偏差|信号周波数偏差 工事担任者,ミニマムポーズ|ミニマムポーズ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -28789,7 +28789,7 @@
       </c>
       <c r="W294" t="inlineStr">
         <is>
-          <t>移動電話端末,漏話減衰量,自動再発信,2回以内,3分</t>
+          <t>漏話減衰量|漏話減衰量 工事担任者,自動再発信|自動再発信 移動電話端末 工事担任者</t>
         </is>
       </c>
     </row>
@@ -28881,7 +28881,7 @@
       </c>
       <c r="W295" t="inlineStr">
         <is>
-          <t>IP電話端末,送出電力,マイナス3dBm,アナログ電話</t>
+          <t>送出電力|送出電力 IP電話端末 工事担任者</t>
         </is>
       </c>
     </row>
@@ -28981,7 +28981,7 @@
       </c>
       <c r="W296" t="inlineStr">
         <is>
-          <t>IP移動電話端末,128秒,通信終了,送信タイミング,総務大臣</t>
+          <t>IP移動電話端末|IP移動電話端末 128秒 工事担任者</t>
         </is>
       </c>
     </row>
@@ -29073,7 +29073,7 @@
       </c>
       <c r="W297" t="inlineStr">
         <is>
-          <t>専用通信回線設備等端末,アクセス制御,変更,デジタルデータ伝送用設備</t>
+          <t>アクセス制御|アクセス制御 専用通信回線 工事担任者</t>
         </is>
       </c>
     </row>
@@ -29178,7 +29178,7 @@
       </c>
       <c r="W298" t="inlineStr">
         <is>
-          <t>絶縁電線,保護物,音声周波,高周波,有線電気通信法</t>
+          <t>絶縁電線|絶縁電線 工事担任者</t>
         </is>
       </c>
     </row>
@@ -29277,7 +29277,7 @@
       </c>
       <c r="W299" t="inlineStr">
         <is>
-          <t>足場金具,1.8メートル,架空電線,離隔距離,30センチメートル</t>
+          <t>足場金具|足場金具 1.8メートル 工事担任者</t>
         </is>
       </c>
     </row>
@@ -29369,7 +29369,7 @@
       </c>
       <c r="W300" t="inlineStr">
         <is>
-          <t>架空電線,道路上,5メートル,有線電気通信設備令</t>
+          <t>架空電線|架空電線 道路上 工事担任者</t>
         </is>
       </c>
     </row>
@@ -29461,7 +29461,7 @@
       </c>
       <c r="W301" t="inlineStr">
         <is>
-          <t>不正アクセス禁止法,電子計算機,犯罪の防止,アクセス制御</t>
+          <t>不正アクセス禁止法|不正アクセス禁止法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -29553,7 +29553,7 @@
       </c>
       <c r="W302" t="inlineStr">
         <is>
-          <t>特定認証業務,電子署名法,本人,主務省令</t>
+          <t>特定認証業務|特定認証業務 工事担任者</t>
         </is>
       </c>
     </row>
@@ -29658,7 +29658,7 @@
       </c>
       <c r="W303" t="inlineStr">
         <is>
-          <t>GE-PON,OLT,TDMA,LLID,DBA,P2MPディスカバリ</t>
+          <t>GE-PON|GE-PON 工事担任者,DBA|DBA 動的帯域割当 工事担任者,LLID|LLID 工事担任者</t>
         </is>
       </c>
     </row>
@@ -29751,7 +29751,7 @@
       </c>
       <c r="W304" t="inlineStr">
         <is>
-          <t>SIPサーバ,レジストラ,プロキシサーバ,リダイレクトサーバ,UAC</t>
+          <t>SIPサーバ|SIPサーバ 工事担任者,レジストラ|レジストラ SIP 工事担任者</t>
         </is>
       </c>
     </row>
@@ -29844,7 +29844,7 @@
       </c>
       <c r="W305" t="inlineStr">
         <is>
-          <t>IEEE802.11ax,Wi-Fi 6,OFDMA,多元接続,2.4GHz,5GHz</t>
+          <t>OFDMA|OFDMA IEEE802.11ax 工事担任者</t>
         </is>
       </c>
     </row>
@@ -29937,7 +29937,7 @@
       </c>
       <c r="W306" t="inlineStr">
         <is>
-          <t>PoE,IEEE802.3at,Type1,Class0,350mA,PSE</t>
+          <t>IEEE802.3at|IEEE802.3at 工事担任者</t>
         </is>
       </c>
     </row>
@@ -30030,7 +30030,7 @@
       </c>
       <c r="W307" t="inlineStr">
         <is>
-          <t>等電位ボンディング,SPD,雷保護,JIS C 5381</t>
+          <t>等電位ボンディング|等電位ボンディング 工事担任者</t>
         </is>
       </c>
     </row>
@@ -30123,7 +30123,7 @@
       </c>
       <c r="W308" t="inlineStr">
         <is>
-          <t>10GBASE-LR,64B/66B,8B/10B,符号化,スクランブル</t>
+          <t>10GBASE-LR|10GBASE-LR 工事担任者,64B/66B|64B/66B 工事担任者</t>
         </is>
       </c>
     </row>
@@ -30213,7 +30213,7 @@
       </c>
       <c r="W309" t="inlineStr">
         <is>
-          <t>FTTB,VDSL,PDS方式,PON,集合住宅</t>
+          <t>FTTB|FTTB 工事担任者,VDSL|VDSL 工事担任者</t>
         </is>
       </c>
     </row>
@@ -30306,7 +30306,7 @@
       </c>
       <c r="W310" t="inlineStr">
         <is>
-          <t>NFV,SDN,仮想化,ルータ,ファイアウォール</t>
+          <t>NFV|NFV 工事担任者,SDN|SDN 工事担任者</t>
         </is>
       </c>
     </row>
@@ -30399,7 +30399,7 @@
       </c>
       <c r="W311" t="inlineStr">
         <is>
-          <t>ホップリミット,IPv6,TTL,ルータ,パケット破棄</t>
+          <t>ホップリミット|ホップリミット IPv6 工事担任者</t>
         </is>
       </c>
     </row>
@@ -30489,7 +30489,7 @@
       </c>
       <c r="W312" t="inlineStr">
         <is>
-          <t>MACアドレス,NIC,FCS,MACフレーム,48ビット</t>
+          <t>MACアドレス|MACアドレス 工事担任者,FCS|FCS 工事担任者</t>
         </is>
       </c>
     </row>
@@ -30582,7 +30582,7 @@
       </c>
       <c r="W313" t="inlineStr">
         <is>
-          <t>バッファオーバフロー,スタック,任意コード実行,脆弱性</t>
+          <t>バッファオーバフロー攻撃|バッファオーバフロー攻撃 工事担任者</t>
         </is>
       </c>
     </row>
@@ -30675,7 +30675,7 @@
       </c>
       <c r="W314" t="inlineStr">
         <is>
-          <t>バイオメトリクス,本人拒否率,他人受入率,しきい値,認証</t>
+          <t>バイオメトリクス認証|バイオメトリクス認証 工事担任者</t>
         </is>
       </c>
     </row>
@@ -30775,7 +30775,7 @@
       </c>
       <c r="W315" t="inlineStr">
         <is>
-          <t>UNIX,root権限,アクセス権限,OS,セキュリティ</t>
+          <t>UNIX|UNIX root権限 工事担任者</t>
         </is>
       </c>
     </row>
@@ -30868,7 +30868,7 @@
       </c>
       <c r="W316" t="inlineStr">
         <is>
-          <t>最小特権の原則,アクセス権限,セキュリティ設計</t>
+          <t>最小特権の原則|最小特権の原則 工事担任者</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="W317" t="inlineStr">
         <is>
-          <t>リスク特定,リスク分析,リスクレベル,ISMS,JIS Q 27001</t>
+          <t>リスク特定|リスク特定 リスク分析 工事担任者</t>
         </is>
       </c>
     </row>
@@ -31064,7 +31064,7 @@
       </c>
       <c r="W318" t="inlineStr">
         <is>
-          <t>光導通試験,SI形,GI形,励振,PINホトダイオード</t>
+          <t>光導通試験|光導通試験 工事担任者</t>
         </is>
       </c>
     </row>
@@ -31140,7 +31140,7 @@
       </c>
       <c r="W319" t="inlineStr">
         <is>
-          <t>JIS C 0303,図記号,情報用アウトレット,電気設備</t>
+          <t>JIS C 0303|JIS C 0303 工事担任者</t>
         </is>
       </c>
     </row>
@@ -31233,7 +31233,7 @@
       </c>
       <c r="W320" t="inlineStr">
         <is>
-          <t>光ファイバケーブル,水平ラック,固定間隔,5メートル,OITDA</t>
+          <t>けん引|光ファイバ 水平ラック固定 工事担任者</t>
         </is>
       </c>
     </row>
@@ -31326,7 +31326,7 @@
       </c>
       <c r="W321" t="inlineStr">
         <is>
-          <t>T568B,RJ-45,ピン8番,茶色,心線配色</t>
+          <t>T568B|T568B 工事担任者</t>
         </is>
       </c>
     </row>
@@ -31424,7 +31424,7 @@
       </c>
       <c r="W322" t="inlineStr">
         <is>
-          <t>インタコネクト,クラスF,水平ケーブル,14m,JIS X 5150</t>
+          <t>JIS X 5150|JIS X 5150 クラスF 工事担任者</t>
         </is>
       </c>
     </row>
@@ -31522,7 +31522,7 @@
       </c>
       <c r="W323" t="inlineStr">
         <is>
-          <t>リバースペア,スプリットペア,クロスペア,配線不良,UTPケーブル</t>
+          <t>リバースペア|リバースペア 配線不良 工事担任者</t>
         </is>
       </c>
     </row>
@@ -31615,7 +31615,7 @@
       </c>
       <c r="W324" t="inlineStr">
         <is>
-          <t>反射減衰量,挿入損失,3.0dB,JIS X 5150</t>
+          <t>JIS X 5150|JIS X 5150 反射減衰量 工事担任者</t>
         </is>
       </c>
     </row>
@@ -31708,7 +31708,7 @@
       </c>
       <c r="W325" t="inlineStr">
         <is>
-          <t>光キャビネット,光ローゼット,ドロップ光ファイバ,インドア光ファイバ</t>
+          <t>光キャビネット|光キャビネット 工事担任者</t>
         </is>
       </c>
     </row>
@@ -31801,7 +31801,7 @@
       </c>
       <c r="W326" t="inlineStr">
         <is>
-          <t>WBGT,暑さ指数,熱中症,湿球黒球温度,熱ストレス</t>
+          <t>WBGT|WBGT 暑さ指数 工事担任者</t>
         </is>
       </c>
     </row>
@@ -31907,7 +31907,7 @@
       </c>
       <c r="W327" t="inlineStr">
         <is>
-          <t>アローダイアグラム,クリティカルパス,トータルフロート,フリーフロート,PERT</t>
+          <t>アローダイアグラム|アローダイアグラム 工事担任者,トータルフロート|トータルフロート 工事担任者,フリーフロート|フリーフロート 工事担任者</t>
         </is>
       </c>
     </row>
@@ -32007,7 +32007,7 @@
       </c>
       <c r="W328" t="inlineStr">
         <is>
-          <t>業務改善命令,通信秘密,差別的取扱い,重要通信,電気通信事業法</t>
+          <t>業務改善命令|業務改善命令 工事担任者</t>
         </is>
       </c>
     </row>
@@ -32102,7 +32102,7 @@
       </c>
       <c r="W329" t="inlineStr">
         <is>
-          <t>資格者証,工事担任者,罰金,5年,養成課程,総務大臣</t>
+          <t>資格者証|資格者証 工事担任者</t>
         </is>
       </c>
     </row>
@@ -32196,7 +32196,7 @@
       </c>
       <c r="W330" t="inlineStr">
         <is>
-          <t>技術基準,責任の分界,設置の場所,電気通信事業法</t>
+          <t>技術基準|技術基準 責任の分界 工事担任者</t>
         </is>
       </c>
     </row>
@@ -32288,7 +32288,7 @@
       </c>
       <c r="W331" t="inlineStr">
         <is>
-          <t>端末設備,異常,電気通信役務,検査,電気通信事業法</t>
+          <t>端末設備|端末設備 異常 工事担任者</t>
         </is>
       </c>
     </row>
@@ -32380,7 +32380,7 @@
       </c>
       <c r="W332" t="inlineStr">
         <is>
-          <t>重要通信,生活基盤,水道,ガス,緊急通信</t>
+          <t>重要通信|重要通信 生活基盤 工事担任者</t>
         </is>
       </c>
     </row>
@@ -32485,7 +32485,7 @@
       </c>
       <c r="W333" t="inlineStr">
         <is>
-          <t>工事担任者,第二級デジタル通信,1Gbps,64kbps,資格区分</t>
+          <t>第二級デジタル通信|第二級デジタル通信 工事担任者</t>
         </is>
       </c>
     </row>
@@ -32584,7 +32584,7 @@
       </c>
       <c r="W334" t="inlineStr">
         <is>
-          <t>資格者証,返納,10日以内,知識及び技術,向上</t>
+          <t>資格者証|資格者証 返納 工事担任者</t>
         </is>
       </c>
     </row>
@@ -32676,7 +32676,7 @@
       </c>
       <c r="W335" t="inlineStr">
         <is>
-          <t>技術基準適合認定,映像面,電磁的方法,表示方法</t>
+          <t>技術基準適合認定|技術基準適合認定 映像面 工事担任者</t>
         </is>
       </c>
     </row>
@@ -32768,7 +32768,7 @@
       </c>
       <c r="W336" t="inlineStr">
         <is>
-          <t>本邦外,有線電気通信設備,電気通信事業者,有線電気通信法</t>
+          <t>有線電気通信法|有線電気通信法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -32860,7 +32860,7 @@
       </c>
       <c r="W337" t="inlineStr">
         <is>
-          <t>非常事態,有線電気通信法,通信確保,命令</t>
+          <t>有線電気通信法|有線電気通信法 非常事態 工事担任者</t>
         </is>
       </c>
     </row>
@@ -32961,7 +32961,7 @@
       </c>
       <c r="W338" t="inlineStr">
         <is>
-          <t>専用通信回線設備等端末,通話チャネル,制御チャネル,端末設備等規則</t>
+          <t>専用通信回線設備等端末|専用通信回線設備等端末 工事担任者,通話チャネル|通話チャネル 工事担任者</t>
         </is>
       </c>
     </row>
@@ -33061,7 +33061,7 @@
       </c>
       <c r="W339" t="inlineStr">
         <is>
-          <t>鳴音,電気的結合,音響的結合,光学的結合,端末設備等規則</t>
+          <t>鳴音|鳴音 電気的 音響的結合 工事担任者</t>
         </is>
       </c>
     </row>
@@ -33154,7 +33154,7 @@
       </c>
       <c r="W340" t="inlineStr">
         <is>
-          <t>配線設備,事業用電気通信設備,損傷,告示,端末設備等規則</t>
+          <t>配線設備|配線設備 損傷防止 工事担任者</t>
         </is>
       </c>
     </row>
@@ -33254,7 +33254,7 @@
       </c>
       <c r="W341" t="inlineStr">
         <is>
-          <t>絶縁抵抗,0.2MΩ,0.4MΩ,300V,配線設備,1MΩ</t>
+          <t>絶縁抵抗|絶縁抵抗 0.2MΩ 0.4MΩ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -33347,7 +33347,7 @@
       </c>
       <c r="W342" t="inlineStr">
         <is>
-          <t>識別符号,無線設備,通信路,端末設備等規則</t>
+          <t>識別符号|識別符号 工事担任者</t>
         </is>
       </c>
     </row>
@@ -33448,7 +33448,7 @@
       </c>
       <c r="W343" t="inlineStr">
         <is>
-          <t>ミニマムポーズ,低群周波数,高群周波数,2周波電力差,押しボタンダイヤル</t>
+          <t>ミニマムポーズ|ミニマムポーズ 工事担任者,低群周波数|低群周波数 高群周波数 工事担任者</t>
         </is>
       </c>
     </row>
@@ -33546,7 +33546,7 @@
       </c>
       <c r="W344" t="inlineStr">
         <is>
-          <t>移動電話端末,応答を確認する信号,端末設備等規則</t>
+          <t>応答を確認する信号|応答を確認する信号 移動電話端末 工事担任者</t>
         </is>
       </c>
     </row>
@@ -33636,7 +33636,7 @@
       </c>
       <c r="W345" t="inlineStr">
         <is>
-          <t>IP電話端末,送出電力,マイナス3dBm,平均レベル</t>
+          <t>送出電力|送出電力 IP電話端末 工事担任者</t>
         </is>
       </c>
     </row>
@@ -33734,7 +33734,7 @@
       </c>
       <c r="W346" t="inlineStr">
         <is>
-          <t>IP移動電話端末,128秒,通信終了メッセージ,応答確認</t>
+          <t>IP移動電話端末|IP移動電話端末 128秒 工事担任者</t>
         </is>
       </c>
     </row>
@@ -33824,7 +33824,7 @@
       </c>
       <c r="W347" t="inlineStr">
         <is>
-          <t>専用通信回線設備等端末,アクセス制御,初期識別符号,ただし書き</t>
+          <t>アクセス制御|アクセス制御 初期識別符号 工事担任者</t>
         </is>
       </c>
     </row>
@@ -33929,7 +33929,7 @@
       </c>
       <c r="W348" t="inlineStr">
         <is>
-          <t>強電流電線,つり線,支線,導体,有線電気通信法</t>
+          <t>強電流電線|強電流電線 定義 工事担任者</t>
         </is>
       </c>
     </row>
@@ -34028,7 +34028,7 @@
       </c>
       <c r="W349" t="inlineStr">
         <is>
-          <t>架空電線,電柱,安全係数,絶縁耐力,有線電気通信設備令</t>
+          <t>電柱|電柱 安全係数 工事担任者</t>
         </is>
       </c>
     </row>
@@ -34120,7 +34120,7 @@
       </c>
       <c r="W350" t="inlineStr">
         <is>
-          <t>有線電気通信設備,絶縁電線,ケーブル,人体危害,有線電気通信設備令</t>
+          <t>有線電気通信設備令|有線電気通信設備令 工事担任者</t>
         </is>
       </c>
     </row>
@@ -34209,7 +34209,7 @@
       </c>
       <c r="W351" t="inlineStr">
         <is>
-          <t>アクセス管理者,不正アクセス禁止法,アクセス制御機能</t>
+          <t>不正アクセス禁止法|不正アクセス禁止法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -34301,7 +34301,7 @@
       </c>
       <c r="W352" t="inlineStr">
         <is>
-          <t>電子署名,電磁的記録,作成,電子署名法</t>
+          <t>電子署名法|電子署名法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -34389,7 +34389,7 @@
       </c>
       <c r="W353" t="inlineStr">
         <is>
-          <t>10G-EPON,GE-PON,デュアルレートバースト受信器,OLT,ONU</t>
+          <t>デュアルレートバースト受信器|デュアルレートバースト受信器 工事担任者</t>
         </is>
       </c>
     </row>
@@ -34482,7 +34482,7 @@
       </c>
       <c r="W354" t="inlineStr">
         <is>
-          <t>VoIPゲートウェイ,デジタル式PBX,IPネットワーク,変換装置</t>
+          <t>VoIPゲートウェイ|VoIPゲートウェイ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -34588,7 +34588,7 @@
       </c>
       <c r="W355" t="inlineStr">
         <is>
-          <t>PoE,Type2,Class4,IEEE802.3at,34.2W,600mA</t>
+          <t>IEEE802.3at|IEEE802.3at Type2 工事担任者</t>
         </is>
       </c>
     </row>
@@ -34681,7 +34681,7 @@
       </c>
       <c r="W356" t="inlineStr">
         <is>
-          <t>IEEE802.11n,IEEE802.11ax,2.4GHz,5GHz,Wi-Fi 6</t>
+          <t>IEEE802.11n|IEEE802.11n 工事担任者</t>
         </is>
       </c>
     </row>
@@ -34774,7 +34774,7 @@
       </c>
       <c r="W357" t="inlineStr">
         <is>
-          <t>電圧スイッチング形SPD,SCR,サイリスタ,ガス入り放電管,サージ防護</t>
+          <t>電圧スイッチング形SPD|電圧スイッチング形SPD 工事担任者</t>
         </is>
       </c>
     </row>
@@ -34867,7 +34867,7 @@
       </c>
       <c r="W358" t="inlineStr">
         <is>
-          <t>PCS,1000BASE-T,物理層,LLCサブレイヤ,PMA</t>
+          <t>PCS|PCS 物理層 工事担任者</t>
         </is>
       </c>
     </row>
@@ -34960,7 +34960,7 @@
       </c>
       <c r="W359" t="inlineStr">
         <is>
-          <t>SS方式,シングルスター,PDS方式,PON,光ファイバ</t>
+          <t>SS方式|SS方式 工事担任者</t>
         </is>
       </c>
     </row>
@@ -35053,7 +35053,7 @@
       </c>
       <c r="W360" t="inlineStr">
         <is>
-          <t>PaaS,SaaS,IaaS,クラウドサービス,ミドルウェア</t>
+          <t>PaaS|PaaS SaaS IaaS 工事担任者</t>
         </is>
       </c>
     </row>
@@ -35151,7 +35151,7 @@
       </c>
       <c r="W361" t="inlineStr">
         <is>
-          <t>IPv6,マルチキャスト,ff,リンクローカル,ユニークローカル</t>
+          <t>IPv6|IPv6 マルチキャスト 工事担任者</t>
         </is>
       </c>
     </row>
@@ -35244,7 +35244,7 @@
       </c>
       <c r="W362" t="inlineStr">
         <is>
-          <t>EoMPLS,LER,MPLS,プリアンブル,SFD,FCS</t>
+          <t>EoMPLS|EoMPLS 工事担任者,MPLS|MPLS 工事担任者</t>
         </is>
       </c>
     </row>
@@ -35337,7 +35337,7 @@
       </c>
       <c r="W363" t="inlineStr">
         <is>
-          <t>パスワードリスト攻撃,辞書攻撃,不正ログイン,認証情報</t>
+          <t>パスワードリスト攻撃|パスワードリスト攻撃 工事担任者</t>
         </is>
       </c>
     </row>
@@ -35430,7 +35430,7 @@
       </c>
       <c r="W364" t="inlineStr">
         <is>
-          <t>シングルサインオン,SSO,リスクベース認証,CHAP,RADIUS</t>
+          <t>シングルサインオン|シングルサインオン 工事担任者</t>
         </is>
       </c>
     </row>
@@ -35520,7 +35520,7 @@
       </c>
       <c r="W365" t="inlineStr">
         <is>
-          <t>スニッフィング,TLS,SMTP,FTP,暗号化</t>
+          <t>スニッフィング|スニッフィング TLS 工事担任者</t>
         </is>
       </c>
     </row>
@@ -35613,7 +35613,7 @@
       </c>
       <c r="W366" t="inlineStr">
         <is>
-          <t>S/MIME,デジタル証明書,電子メール,暗号化,デジタル署名</t>
+          <t>S/MIME|S/MIME 工事担任者</t>
         </is>
       </c>
     </row>
@@ -35719,7 +35719,7 @@
       </c>
       <c r="W367" t="inlineStr">
         <is>
-          <t>JIS Q 27001,機密性,完全性,可用性,CIA,情報分類</t>
+          <t>JIS Q 27001|JIS Q 27001 工事担任者</t>
         </is>
       </c>
     </row>
@@ -35795,7 +35795,7 @@
       </c>
       <c r="W368" t="inlineStr">
         <is>
-          <t>JIS C 0303,複合アウトレット,図記号,電気設備</t>
+          <t>JIS C 0303|JIS C 0303 工事担任者</t>
         </is>
       </c>
     </row>
@@ -35896,7 +35896,7 @@
       </c>
       <c r="W369" t="inlineStr">
         <is>
-          <t>融着接続,アーク放電,スクリーニング試験,引張試験,端面切断</t>
+          <t>融着接続|融着接続 アーク放電 工事担任者</t>
         </is>
       </c>
     </row>
@@ -35989,7 +35989,7 @@
       </c>
       <c r="W370" t="inlineStr">
         <is>
-          <t>交差接続,クロスコネクト,光配線盤,ジャンパコード</t>
+          <t>交差接続|交差接続 工事担任者</t>
         </is>
       </c>
     </row>
@@ -36095,7 +36095,7 @@
       </c>
       <c r="W371" t="inlineStr">
         <is>
-          <t>挿入損失,直流ループ抵抗,UTPケーブル,測定,JIS X 5150</t>
+          <t>挿入損失|挿入損失 測定方法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -36193,7 +36193,7 @@
       </c>
       <c r="W372" t="inlineStr">
         <is>
-          <t>クロスコネクト,クラスE,水平ケーブル,80.5m,JIS X 5150</t>
+          <t>JIS X 5150|JIS X 5150 工事担任者</t>
         </is>
       </c>
     </row>
@@ -36286,7 +36286,7 @@
       </c>
       <c r="W373" t="inlineStr">
         <is>
-          <t>フラット型インドア光ケーブル,露出配線,固定ピン,カーペット下</t>
+          <t>フラット型インドア光ケーブル|フラット型インドア光ケーブル 工事担任者</t>
         </is>
       </c>
     </row>
@@ -36387,7 +36387,7 @@
       </c>
       <c r="W374" t="inlineStr">
         <is>
-          <t>反射減衰量,クラスA,クラスB,JIS X 5150</t>
+          <t>JIS X 5150|JIS X 5150 クラスA クラスB 工事担任者</t>
         </is>
       </c>
     </row>
@@ -36480,7 +36480,7 @@
       </c>
       <c r="W375" t="inlineStr">
         <is>
-          <t>キンク,UTPケーブル,くの字型変形,ケーブル布設</t>
+          <t>キンク|キンク UTPケーブル 工事担任者</t>
         </is>
       </c>
     </row>
@@ -36570,7 +36570,7 @@
       </c>
       <c r="W376" t="inlineStr">
         <is>
-          <t>シューハート管理図,3シグマ,管理限界線,QC,統計的品質管理</t>
+          <t>シューハート管理図|シューハート管理図 工事担任者</t>
         </is>
       </c>
     </row>
@@ -36676,7 +36676,7 @@
       </c>
       <c r="W377" t="inlineStr">
         <is>
-          <t>クリティカルパス,トータルフロート,アローダイアグラム,PERT</t>
+          <t>クリティカルパス|クリティカルパス 工事担任者</t>
         </is>
       </c>
     </row>
@@ -36781,7 +36781,7 @@
       </c>
       <c r="W378" t="inlineStr">
         <is>
-          <t>端末設備,接続請求,利用者,著しく不適当,電気通信事業法</t>
+          <t>端末設備|端末設備 接続請求 工事担任者</t>
         </is>
       </c>
     </row>
@@ -36873,7 +36873,7 @@
       </c>
       <c r="W379" t="inlineStr">
         <is>
-          <t>自営電気通信設備,保持,経営上困難,接続拒否,総務大臣</t>
+          <t>自営電気通信設備|自営電気通信設備 保持 工事担任者</t>
         </is>
       </c>
     </row>
@@ -36965,7 +36965,7 @@
       </c>
       <c r="W380" t="inlineStr">
         <is>
-          <t>技術基準適合認定,表示,電気通信事業法</t>
+          <t>技術基準適合認定|技術基準適合認定 工事担任者</t>
         </is>
       </c>
     </row>
@@ -37057,7 +37057,7 @@
       </c>
       <c r="W381" t="inlineStr">
         <is>
-          <t>業務改善命令,重要通信,適切に配慮,電気通信事業法</t>
+          <t>業務改善命令|業務改善命令 重要通信 工事担任者</t>
         </is>
       </c>
     </row>
@@ -37156,7 +37156,7 @@
       </c>
       <c r="W382" t="inlineStr">
         <is>
-          <t>重要通信,治安,天災,新聞社,緊急通信</t>
+          <t>重要通信|重要通信 治安 工事担任者</t>
         </is>
       </c>
     </row>
@@ -37246,7 +37246,7 @@
       </c>
       <c r="W383" t="inlineStr">
         <is>
-          <t>工事担任者,第一級アナログ通信,第二級デジタル通信,資格区分</t>
+          <t>工事担任者資格区分|工事担任者 資格区分 比較</t>
         </is>
       </c>
     </row>
@@ -37340,7 +37340,7 @@
       </c>
       <c r="W384" t="inlineStr">
         <is>
-          <t>資格者証,技術の向上,書換え交付,再交付,住所変更</t>
+          <t>資格者証|資格者証 書換え交付 工事担任者</t>
         </is>
       </c>
     </row>
@@ -37429,7 +37429,7 @@
       </c>
       <c r="W385" t="inlineStr">
         <is>
-          <t>技術基準適合認定,映像面,電磁的方法,取扱説明書,表示方法</t>
+          <t>技術基準適合認定|技術基準適合認定 表示方法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -37521,7 +37521,7 @@
       </c>
       <c r="W386" t="inlineStr">
         <is>
-          <t>有線電気通信法,総務大臣,報告,立入検査</t>
+          <t>有線電気通信法|有線電気通信法 立入検査 工事担任者</t>
         </is>
       </c>
     </row>
@@ -37613,7 +37613,7 @@
       </c>
       <c r="W387" t="inlineStr">
         <is>
-          <t>有線電気通信設備,方式の別,設置の場所,2週間前,届出</t>
+          <t>有線電気通信設備令|有線電気通信設備令 変更届 工事担任者</t>
         </is>
       </c>
     </row>
@@ -37718,7 +37718,7 @@
       </c>
       <c r="W388" t="inlineStr">
         <is>
-          <t>デジタルデータ伝送用設備,総合デジタル通信用設備,64kbps,端末設備等規則</t>
+          <t>デジタルデータ伝送用設備|デジタルデータ伝送用設備 工事担任者</t>
         </is>
       </c>
     </row>
@@ -37810,7 +37810,7 @@
       </c>
       <c r="W389" t="inlineStr">
         <is>
-          <t>端末設備,事業用電気通信設備,識別機能,漏えい</t>
+          <t>識別機能|識別機能 漏えい 工事担任者</t>
         </is>
       </c>
     </row>
@@ -37907,7 +37907,7 @@
       </c>
       <c r="W390" t="inlineStr">
         <is>
-          <t>接地抵抗,100オーム,端末設備等規則</t>
+          <t>接地抵抗|接地抵抗 工事担任者</t>
         </is>
       </c>
     </row>
@@ -38006,7 +38006,7 @@
       </c>
       <c r="W391" t="inlineStr">
         <is>
-          <t>配線設備,強電流電線,有線電気通信設備令,評価雑音電力,マイナス58dB</t>
+          <t>有線電気通信設備令|有線電気通信設備令 評価雑音電力 工事担任者</t>
         </is>
       </c>
     </row>
@@ -38098,7 +38098,7 @@
       </c>
       <c r="W392" t="inlineStr">
         <is>
-          <t>識別符号,無線設備,空き周波数,通信路</t>
+          <t>識別符号|識別符号 空き周波数 工事担任者</t>
         </is>
       </c>
     </row>
@@ -38203,7 +38203,7 @@
       </c>
       <c r="W393" t="inlineStr">
         <is>
-          <t>押しボタンダイヤル,信号送出時間,50ms,30ms,ミニマムポーズ</t>
+          <t>信号送出時間|信号送出時間 50ms 工事担任者</t>
         </is>
       </c>
     </row>
@@ -38298,7 +38298,7 @@
       </c>
       <c r="W394" t="inlineStr">
         <is>
-          <t>移動電話端末,自動再発信,2回以内,3分,チャネル切断</t>
+          <t>自動再発信|自動再発信 移動電話端末 工事担任者</t>
         </is>
       </c>
     </row>
@@ -38387,7 +38387,7 @@
       </c>
       <c r="W395" t="inlineStr">
         <is>
-          <t>IP電話端末,直流電圧,緊急通報,電気通信回線</t>
+          <t>IP電話端末|IP電話端末 緊急通報 工事担任者</t>
         </is>
       </c>
     </row>
@@ -38481,7 +38481,7 @@
       </c>
       <c r="W396" t="inlineStr">
         <is>
-          <t>IP移動電話端末,128秒,送信タイミング,総務大臣,告示</t>
+          <t>IP移動電話端末|IP移動電話端末 送信タイミング 工事担任者</t>
         </is>
       </c>
     </row>
@@ -38578,7 +38578,7 @@
       </c>
       <c r="W397" t="inlineStr">
         <is>
-          <t>専用通信回線設備等端末,漏話減衰量,1500Hz,70dB</t>
+          <t>漏話減衰量|漏話減衰量 工事担任者</t>
         </is>
       </c>
     </row>
@@ -38683,7 +38683,7 @@
       </c>
       <c r="W398" t="inlineStr">
         <is>
-          <t>通信回線,線路の電圧,100ボルト,平衡度,有線電気通信設備令</t>
+          <t>通信回線|通信回線 線路の電圧 工事担任者</t>
         </is>
       </c>
     </row>
@@ -38775,7 +38775,7 @@
       </c>
       <c r="W399" t="inlineStr">
         <is>
-          <t>強電流電線,重畳,分離,開閉,有線電気通信設備令</t>
+          <t>強電流電線|強電流電線 重畳 工事担任者</t>
         </is>
       </c>
     </row>
@@ -38869,7 +38869,7 @@
       </c>
       <c r="W400" t="inlineStr">
         <is>
-          <t>屋内電線,強電流ケーブル,離隔距離,隔壁,有線電気通信設備令</t>
+          <t>屋内電線|屋内電線 強電流ケーブル 工事担任者</t>
         </is>
       </c>
     </row>
@@ -38968,7 +38968,7 @@
       </c>
       <c r="W401" t="inlineStr">
         <is>
-          <t>識別符号,不正アクセス禁止法,署名,アクセス管理者</t>
+          <t>識別符号|識別符号 不正アクセス禁止法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -39060,7 +39060,7 @@
       </c>
       <c r="W402" t="inlineStr">
         <is>
-          <t>認証業務,電子署名法,電子署名,自らが行う</t>
+          <t>認証業務|認証業務 電子署名法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -39150,7 +39150,7 @@
       </c>
       <c r="W403" t="inlineStr">
         <is>
-          <t>10G-EPON,GE-PON,TDMA,WDM,OLT,ONU</t>
+          <t>10G-EPON|10G-EPON GE-PON 工事担任者,WDM|WDM 工事担任者</t>
         </is>
       </c>
     </row>
@@ -39243,7 +39243,7 @@
       </c>
       <c r="W404" t="inlineStr">
         <is>
-          <t>SIPサーバ,ロケーションサーバ,レジストラ,UAC,位置情報</t>
+          <t>ロケーションサーバ|ロケーションサーバ SIP 工事担任者</t>
         </is>
       </c>
     </row>
@@ -39331,7 +39331,7 @@
       </c>
       <c r="W405" t="inlineStr">
         <is>
-          <t>PoE,オルタナティブB,ピン4・5・7・8,予備ペア,1000BASE-T</t>
+          <t>PoEオルタナティブB|PoE オルタナティブB 工事担任者</t>
         </is>
       </c>
     </row>
@@ -39424,7 +39424,7 @@
       </c>
       <c r="W406" t="inlineStr">
         <is>
-          <t>IEEE802.11ax,Wi-Fi 6,6GHz,ISMバンド,気象レーダ</t>
+          <t>IEEE802.11ax|IEEE802.11ax 6GHz 工事担任者</t>
         </is>
       </c>
     </row>
@@ -39524,7 +39524,7 @@
       </c>
       <c r="W407" t="inlineStr">
         <is>
-          <t>コモンモードチョークコイル,フェライトコア,高周波,ノイズ対策,EMC</t>
+          <t>コモンモードチョークコイル|コモンモードチョークコイル 工事担任者,フェライトコア|フェライトコア 工事担任者</t>
         </is>
       </c>
     </row>
@@ -39617,7 +39617,7 @@
       </c>
       <c r="W408" t="inlineStr">
         <is>
-          <t>1000BASE-T,8B1Q4,4D-PAM5,NRZI,8B/10B,符号化</t>
+          <t>8B1Q4|8B1Q4 工事担任者</t>
         </is>
       </c>
     </row>
@@ -39710,7 +39710,7 @@
       </c>
       <c r="W409" t="inlineStr">
         <is>
-          <t>FM一括変換方式,CATV,光強度変調,3GHz,映像信号</t>
+          <t>FM一括変換方式|FM一括変換方式 工事担任者</t>
         </is>
       </c>
     </row>
@@ -39803,7 +39803,7 @@
       </c>
       <c r="W410" t="inlineStr">
         <is>
-          <t>ICMPv6,パラメータ問題,時間超過,終点到達不能,IPv6</t>
+          <t>ICMPv6|ICMPv6 パラメータ問題 工事担任者</t>
         </is>
       </c>
     </row>
@@ -39896,7 +39896,7 @@
       </c>
       <c r="W411" t="inlineStr">
         <is>
-          <t>ジッタバッファ,揺らぎ吸収,VoIP,音声品質,パケット損失</t>
+          <t>ジッタバッファ|ジッタバッファ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -39986,7 +39986,7 @@
       </c>
       <c r="W412" t="inlineStr">
         <is>
-          <t>広域イーサネット,MPLS,LER,LSR,レイヤ2</t>
+          <t>広域イーサネット|広域イーサネット 工事担任者,MPLS|MPLS LER LSR 工事担任者</t>
         </is>
       </c>
     </row>
@@ -40079,7 +40079,7 @@
       </c>
       <c r="W413" t="inlineStr">
         <is>
-          <t>rootkit,ルートキット,バックドア,権限奪取,マルウェア</t>
+          <t>rootkit|rootkit 工事担任者</t>
         </is>
       </c>
     </row>
@@ -40179,7 +40179,7 @@
       </c>
       <c r="W414" t="inlineStr">
         <is>
-          <t>ハイブリッド暗号,PGP,共通鍵暗号,公開鍵暗号,処理速度</t>
+          <t>ハイブリッド暗号|ハイブリッド暗号 PGP 工事担任者</t>
         </is>
       </c>
     </row>
@@ -40275,7 +40275,7 @@
       </c>
       <c r="W415" t="inlineStr">
         <is>
-          <t>クロスサイトスクリプティング,XSS,SQLインジェクション,サニタイジング</t>
+          <t>クロスサイトスクリプティング|クロスサイトスクリプティング 工事担任者</t>
         </is>
       </c>
     </row>
@@ -40375,7 +40375,7 @@
       </c>
       <c r="W416" t="inlineStr">
         <is>
-          <t>IPsec,トランスポートモード,トンネルモード,VPN,リモートアクセス</t>
+          <t>IPsec|IPsec 工事担任者</t>
         </is>
       </c>
     </row>
@@ -40468,7 +40468,7 @@
       </c>
       <c r="W417" t="inlineStr">
         <is>
-          <t>CSIRT,インシデント対応,セキュリティ,被害拡大防止</t>
+          <t>CSIRT|CSIRT 工事担任者</t>
         </is>
       </c>
     </row>
@@ -40574,7 +40574,7 @@
       </c>
       <c r="W418" t="inlineStr">
         <is>
-          <t>融着接続,アーク放電,スクリーニング試験,引張試験,端面切断</t>
+          <t>融着接続|融着接続 工事担任者</t>
         </is>
       </c>
     </row>
@@ -40667,7 +40667,7 @@
       </c>
       <c r="W419" t="inlineStr">
         <is>
-          <t>フリーアクセスフロア,OAフロア,不陸調整,支柱ねじ</t>
+          <t>フリーアクセスフロア|フリーアクセスフロア 工事担任者</t>
         </is>
       </c>
     </row>
@@ -40757,7 +40757,7 @@
       </c>
       <c r="W420" t="inlineStr">
         <is>
-          <t>OTDR法,後方散乱光,光ファイバ損失,両端測定,JIS C 6823</t>
+          <t>OTDR法|OTDR法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -40850,7 +40850,7 @@
       </c>
       <c r="W421" t="inlineStr">
         <is>
-          <t>T568B,RJ-45,ピン6番,緑色,心線配色</t>
+          <t>T568B|T568B 工事担任者</t>
         </is>
       </c>
     </row>
@@ -40948,7 +40948,7 @@
       </c>
       <c r="W422" t="inlineStr">
         <is>
-          <t>インタコネクト,クラスF,水平ケーブル,82.5m,JIS X 5150</t>
+          <t>JIS X 5150|JIS X 5150 クラスF 工事担任者</t>
         </is>
       </c>
     </row>
@@ -41041,7 +41041,7 @@
       </c>
       <c r="W423" t="inlineStr">
         <is>
-          <t>IEEE802.3bq,40GBASE-T,カテゴリ8,30メートル,データセンタ</t>
+          <t>IEEE802.3bq|IEEE802.3bq 40GBASE-T 工事担任者</t>
         </is>
       </c>
     </row>
@@ -41134,7 +41134,7 @@
       </c>
       <c r="W424" t="inlineStr">
         <is>
-          <t>OTDR,ダイナミックレンジ,後方散乱光,パルスパワー</t>
+          <t>OTDRダイナミックレンジ|OTDR ダイナミックレンジ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -41227,7 +41227,7 @@
       </c>
       <c r="W425" t="inlineStr">
         <is>
-          <t>融着接続,気泡,光ファイバカッタ,端面切断,やり直し</t>
+          <t>融着接続|融着接続 気泡 工事担任者</t>
         </is>
       </c>
     </row>
@@ -41328,7 +41328,7 @@
       </c>
       <c r="W426" t="inlineStr">
         <is>
-          <t>ヒストグラム,散布図,パレート図,管理図,QC7つ道具</t>
+          <t>QC7つ道具|QC7つ道具 工事担任者</t>
         </is>
       </c>
     </row>
@@ -41421,7 +41421,7 @@
       </c>
       <c r="W427" t="inlineStr">
         <is>
-          <t>KYT,危険予知訓練,4ラウンド法,本質追究,安全管理</t>
+          <t>KYT|KYT 4ラウンド法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -41521,7 +41521,7 @@
       </c>
       <c r="W428" t="inlineStr">
         <is>
-          <t>資格者証,工事担任者,罰金,5年,養成課程,返納</t>
+          <t>資格者証|資格者証 罰金 5年 工事担任者</t>
         </is>
       </c>
     </row>
@@ -41620,7 +41620,7 @@
       </c>
       <c r="W429" t="inlineStr">
         <is>
-          <t>業務改善命令,支障,おそれ,提供条件,電気通信事業法</t>
+          <t>業務改善命令|業務改善命令 支障 工事担任者</t>
         </is>
       </c>
     </row>
@@ -41719,7 +41719,7 @@
       </c>
       <c r="W430" t="inlineStr">
         <is>
-          <t>管理規程,事業開始前,届出,基礎的電気通信役務,電気通信事業法</t>
+          <t>管理規程|管理規程 届出 工事担任者</t>
         </is>
       </c>
     </row>
@@ -41811,7 +41811,7 @@
       </c>
       <c r="W431" t="inlineStr">
         <is>
-          <t>技術基準適合認定,表示,他の利用者,妨害防止</t>
+          <t>技術基準適合認定|技術基準適合認定 工事担任者</t>
         </is>
       </c>
     </row>
@@ -41903,7 +41903,7 @@
       </c>
       <c r="W432" t="inlineStr">
         <is>
-          <t>端末設備,接続請求,利用者,著しく不適当,電気通信事業法</t>
+          <t>端末設備|端末設備 接続請求 工事担任者</t>
         </is>
       </c>
     </row>
@@ -42008,7 +42008,7 @@
       </c>
       <c r="W433" t="inlineStr">
         <is>
-          <t>工事担任者,第二級アナログ通信,1以下,50以下,資格区分</t>
+          <t>第二級アナログ通信|第二級アナログ通信 工事担任者</t>
         </is>
       </c>
     </row>
@@ -42107,7 +42107,7 @@
       </c>
       <c r="W434" t="inlineStr">
         <is>
-          <t>資格者証,再交付,汚した,返納,10日以内</t>
+          <t>資格者証|資格者証 再交付 返納 工事担任者</t>
         </is>
       </c>
     </row>
@@ -42196,7 +42196,7 @@
       </c>
       <c r="W435" t="inlineStr">
         <is>
-          <t>技術基準適合認定番号,固定電話端末,G,専用通信回線設備等端末,P</t>
+          <t>技術基準適合認定番号|技術基準適合認定番号 工事担任者</t>
         </is>
       </c>
     </row>
@@ -42301,7 +42301,7 @@
       </c>
       <c r="W436" t="inlineStr">
         <is>
-          <t>有線電気通信法,設置及び使用,秩序,公共の福祉</t>
+          <t>有線電気通信法|有線電気通信法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -42388,7 +42388,7 @@
       </c>
       <c r="W437" t="inlineStr">
         <is>
-          <t>有線電気通信設備,変更届,2週間前,工事を要しない,2週間以内</t>
+          <t>有線電気通信設備令|有線電気通信設備令 変更届 工事担任者</t>
         </is>
       </c>
     </row>
@@ -42493,7 +42493,7 @@
       </c>
       <c r="W438" t="inlineStr">
         <is>
-          <t>IP移動電話端末,IP移動電話用設備,デジタルデータ伝送用設備,端末設備等規則</t>
+          <t>IP移動電話端末|IP移動電話端末 工事担任者</t>
         </is>
       </c>
     </row>
@@ -42592,7 +42592,7 @@
       </c>
       <c r="W439" t="inlineStr">
         <is>
-          <t>分界点,電気的条件,光学的条件,鳴音,事業用電気通信設備</t>
+          <t>分界点|分界点 接続方式 工事担任者</t>
         </is>
       </c>
     </row>
@@ -42684,7 +42684,7 @@
       </c>
       <c r="W440" t="inlineStr">
         <is>
-          <t>絶縁耐力試験,250V,2500ボルト,1分間,端末設備等規則</t>
+          <t>絶縁耐力試験|絶縁耐力試験 2500V 工事担任者</t>
         </is>
       </c>
     </row>
@@ -42776,7 +42776,7 @@
       </c>
       <c r="W441" t="inlineStr">
         <is>
-          <t>配線設備,絶縁抵抗,直流200V,1MΩ,端末設備等規則</t>
+          <t>配線設備|配線設備 直流200V 工事担任者</t>
         </is>
       </c>
     </row>
@@ -42868,7 +42868,7 @@
       </c>
       <c r="W442" t="inlineStr">
         <is>
-          <t>識別符号,無線設備,通信路,照合,端末設備等規則</t>
+          <t>識別符号|識別符号 工事担任者</t>
         </is>
       </c>
     </row>
@@ -42960,7 +42960,7 @@
       </c>
       <c r="W443" t="inlineStr">
         <is>
-          <t>移動電話端末,チャネル切断,通信終了,端末設備等規則</t>
+          <t>チャネル切断|チャネル切断 移動電話端末 工事担任者</t>
         </is>
       </c>
     </row>
@@ -43065,7 +43065,7 @@
       </c>
       <c r="W444" t="inlineStr">
         <is>
-          <t>固定電話端末,自動再発信,3分間,2回以内</t>
+          <t>自動再発信|自動再発信 固定電話端末 工事担任者</t>
         </is>
       </c>
     </row>
@@ -43164,7 +43164,7 @@
       </c>
       <c r="W445" t="inlineStr">
         <is>
-          <t>専用通信回線設備等端末,直流電圧,電気的条件,光学的条件</t>
+          <t>専用通信回線設備等端末|専用通信回線設備等端末 直流電圧 工事担任者</t>
         </is>
       </c>
     </row>
@@ -43264,7 +43264,7 @@
       </c>
       <c r="W446" t="inlineStr">
         <is>
-          <t>アクセス制御,初期識別符号,ソフトウェア更新,通信プロトコル,電力停止</t>
+          <t>アクセス制御|アクセス制御 ソフトウェア更新 工事担任者</t>
         </is>
       </c>
     </row>
@@ -43363,7 +43363,7 @@
       </c>
       <c r="W447" t="inlineStr">
         <is>
-          <t>2周波電力差,5dB,ミニマムポーズ,最小値,押しボタンダイヤル</t>
+          <t>2周波電力差|2周波電力差 ミニマムポーズ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -43452,7 +43452,7 @@
       </c>
       <c r="W448" t="inlineStr">
         <is>
-          <t>屋内電線,強電流電線,30センチメートル,保安機能,有線電気通信設備令</t>
+          <t>屋内電線|屋内電線 強電流電線 工事担任者</t>
         </is>
       </c>
     </row>
@@ -43557,7 +43557,7 @@
       </c>
       <c r="W449" t="inlineStr">
         <is>
-          <t>架空電線,建造物,離隔距離,30センチメートル,有線電気通信設備令</t>
+          <t>架空電線|架空電線 建造物 工事担任者</t>
         </is>
       </c>
     </row>
@@ -43649,7 +43649,7 @@
       </c>
       <c r="W450" t="inlineStr">
         <is>
-          <t>架空電線,鉄道横断,軌条面,6メートル,有線電気通信設備令</t>
+          <t>架空電線|架空電線 鉄道横断 工事担任者</t>
         </is>
       </c>
     </row>
@@ -43741,7 +43741,7 @@
       </c>
       <c r="W451" t="inlineStr">
         <is>
-          <t>不正アクセス禁止法,電子計算機,犯罪の防止,アクセス制御</t>
+          <t>不正アクセス禁止法|不正アクセス禁止法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -43833,7 +43833,7 @@
       </c>
       <c r="W452" t="inlineStr">
         <is>
-          <t>電子署名,電磁的記録,作成,電子署名法</t>
+          <t>電子署名法|電子署名法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -43926,7 +43926,7 @@
       </c>
       <c r="W453" t="inlineStr">
         <is>
-          <t>XGS-PON,ITU-T G.9807.1,GTCフレーム,10Gbps,XG-PON</t>
+          <t>XGS-PON|XGS-PON 工事担任者</t>
         </is>
       </c>
     </row>
@@ -44026,7 +44026,7 @@
       </c>
       <c r="W454" t="inlineStr">
         <is>
-          <t>汎用サーバIP-PBX,VoIPゲートウェイ,アナログ電話機,SIP,アプリケーション層</t>
+          <t>IP-PBX|IP-PBX VoIPゲートウェイ 工事担任者,SIP|SIP アプリケーション層 工事担任者</t>
         </is>
       </c>
     </row>
@@ -44119,7 +44119,7 @@
       </c>
       <c r="W455" t="inlineStr">
         <is>
-          <t>IEEE802.3bt,Type4,Class8,90W,PoE,4対</t>
+          <t>IEEE802.3bt|IEEE802.3bt 工事担任者</t>
         </is>
       </c>
     </row>
@@ -44212,7 +44212,7 @@
       </c>
       <c r="W456" t="inlineStr">
         <is>
-          <t>IEEE802.11n,ブロックACK,プローブ応答,ビーコン,フレーム</t>
+          <t>ブロックACK|ブロックACK IEEE802.11n 工事担任者</t>
         </is>
       </c>
     </row>
@@ -44305,7 +44305,7 @@
       </c>
       <c r="W457" t="inlineStr">
         <is>
-          <t>等電位ボンディング,SPD,雷保護,直接導体,JIS C 5381</t>
+          <t>等電位ボンディング|等電位ボンディング 工事担任者</t>
         </is>
       </c>
     </row>
@@ -44398,7 +44398,7 @@
       </c>
       <c r="W458" t="inlineStr">
         <is>
-          <t>10GBASE-LR,64B/66B,4B/5B,8B1Q4,8B/6T,符号化</t>
+          <t>10GBASE-LR|10GBASE-LR 工事担任者,64B/66B|64B/66B 工事担任者</t>
         </is>
       </c>
     </row>
@@ -44491,7 +44491,7 @@
       </c>
       <c r="W459" t="inlineStr">
         <is>
-          <t>HFC,Hybrid Fiber Coaxial,光ノード,同軸ケーブル,FTTH</t>
+          <t>HFC|HFC 工事担任者</t>
         </is>
       </c>
     </row>
@@ -44584,7 +44584,7 @@
       </c>
       <c r="W460" t="inlineStr">
         <is>
-          <t>SaaS,PaaS,IaaS,クラウドサービス,アプリケーション</t>
+          <t>SaaS|SaaS PaaS IaaS 工事担任者</t>
         </is>
       </c>
     </row>
@@ -44685,7 +44685,7 @@
       </c>
       <c r="W461" t="inlineStr">
         <is>
-          <t>IPv6,リンクローカル,fe80,fec0,マルチキャスト,エニーキャスト</t>
+          <t>IPv6|IPv6 リンクローカル 工事担任者</t>
         </is>
       </c>
     </row>
@@ -44775,7 +44775,7 @@
       </c>
       <c r="W462" t="inlineStr">
         <is>
-          <t>MACアドレス,NIC,FCS,MACフレーム,48ビット</t>
+          <t>MACアドレス|MACアドレス 工事担任者,FCS|FCS 工事担任者</t>
         </is>
       </c>
     </row>
@@ -44868,7 +44868,7 @@
       </c>
       <c r="W463" t="inlineStr">
         <is>
-          <t>検疫ネットワーク,セキュリティポリシー,隔離,不正PC</t>
+          <t>検疫ネットワーク|検疫ネットワーク 工事担任者</t>
         </is>
       </c>
     </row>
@@ -44961,7 +44961,7 @@
       </c>
       <c r="W464" t="inlineStr">
         <is>
-          <t>DKIM,SPF,デジタル署名,送信元ドメイン認証,迷惑メール</t>
+          <t>DKIM|DKIM SPF 工事担任者</t>
         </is>
       </c>
     </row>
@@ -45054,7 +45054,7 @@
       </c>
       <c r="W465" t="inlineStr">
         <is>
-          <t>SSH,Secure Shell,Telnet,暗号化,遠隔操作</t>
+          <t>SSH|SSH Telnet 工事担任者</t>
         </is>
       </c>
     </row>
@@ -45154,7 +45154,7 @@
       </c>
       <c r="W466" t="inlineStr">
         <is>
-          <t>スニッフィング,データマイニング,IPスプーフィング,なりすまし</t>
+          <t>スニッフィング|スニッフィング IPスプーフィング 工事担任者</t>
         </is>
       </c>
     </row>
@@ -45260,7 +45260,7 @@
       </c>
       <c r="W467" t="inlineStr">
         <is>
-          <t>ISMS,JIS Q 27001,開発環境,テスト環境,本番環境,分離</t>
+          <t>JIS Q 27001|JIS Q 27001 工事担任者</t>
         </is>
       </c>
     </row>
@@ -45353,7 +45353,7 @@
       </c>
       <c r="W468" t="inlineStr">
         <is>
-          <t>挿入法,カットバック法,挿入損失,融着接続,JIS C 6823</t>
+          <t>挿入法|挿入法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -45429,7 +45429,7 @@
       </c>
       <c r="W469" t="inlineStr">
         <is>
-          <t>JIS C 0303,情報用アウトレット,図記号,電気設備</t>
+          <t>JIS C 0303|JIS C 0303 工事担任者</t>
         </is>
       </c>
     </row>
@@ -45522,7 +45522,7 @@
       </c>
       <c r="W470" t="inlineStr">
         <is>
-          <t>キンク,UTPケーブル,くの字型,ケーブル布設,変形</t>
+          <t>キンク|キンク UTPケーブル 工事担任者</t>
         </is>
       </c>
     </row>
@@ -45612,7 +45612,7 @@
       </c>
       <c r="W471" t="inlineStr">
         <is>
-          <t>光ファイバケーブル,テンションメンバ,8の字,同心円,けん引端</t>
+          <t>8の字巻き|光ファイバ 8の字巻き 工事担任者</t>
         </is>
       </c>
     </row>
@@ -45713,7 +45713,7 @@
       </c>
       <c r="W472" t="inlineStr">
         <is>
-          <t>分岐点,フロア配線盤,15メートル,JIS X 5150,水平配線</t>
+          <t>分岐点|分岐点 フロア配線盤 工事担任者</t>
         </is>
       </c>
     </row>
@@ -45806,7 +45806,7 @@
       </c>
       <c r="W473" t="inlineStr">
         <is>
-          <t>エイリアンクロストーク,異線間漏話,ラック内余長,UTPケーブル</t>
+          <t>エイリアンクロストーク|エイリアンクロストーク 工事担任者</t>
         </is>
       </c>
     </row>
@@ -45899,7 +45899,7 @@
       </c>
       <c r="W474" t="inlineStr">
         <is>
-          <t>FASコネクタ,単心光コネクタ,架空クロージャ,ドロップ光ファイバ</t>
+          <t>FASコネクタ|FASコネクタ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -45992,7 +45992,7 @@
       </c>
       <c r="W475" t="inlineStr">
         <is>
-          <t>STP,IEEE802.1D,スパニングツリー,ループ防止,フレーム</t>
+          <t>STP|STP IEEE802.1D 工事担任者</t>
         </is>
       </c>
     </row>
@@ -46103,7 +46103,7 @@
       </c>
       <c r="W476" t="inlineStr">
         <is>
-          <t>変動原価率,損益分岐点,採算性,コスト管理,工事</t>
+          <t>損益分岐点|損益分岐点 変動原価率 工事担任者</t>
         </is>
       </c>
     </row>
@@ -46201,7 +46201,7 @@
       </c>
       <c r="W477" t="inlineStr">
         <is>
-          <t>アローダイアグラム,クリティカルパス,短縮,所要日数,PERT</t>
+          <t>アローダイアグラム|アローダイアグラム 工事担任者</t>
         </is>
       </c>
     </row>
@@ -46306,7 +46306,7 @@
       </c>
       <c r="W478" t="inlineStr">
         <is>
-          <t>業務改善命令,支障,おそれ,不当差別,電気通信事業法</t>
+          <t>業務改善命令|業務改善命令 工事担任者</t>
         </is>
       </c>
     </row>
@@ -46398,7 +46398,7 @@
       </c>
       <c r="W479" t="inlineStr">
         <is>
-          <t>端末設備,異常,電気通信役務,検査,電気通信事業法</t>
+          <t>端末設備|端末設備 異常 工事担任者</t>
         </is>
       </c>
     </row>
@@ -46495,7 +46495,7 @@
       </c>
       <c r="W480" t="inlineStr">
         <is>
-          <t>管理規程,確実かつ安定的,適正かつ継続的,電気通信事業法</t>
+          <t>管理規程|管理規程 確実かつ安定的 工事担任者</t>
         </is>
       </c>
     </row>
@@ -46594,7 +46594,7 @@
       </c>
       <c r="W481" t="inlineStr">
         <is>
-          <t>技術基準適合認定,登録認定機関,総務省令,表示,公示</t>
+          <t>技術基準適合認定|技術基準適合認定 工事担任者</t>
         </is>
       </c>
     </row>
@@ -46689,7 +46689,7 @@
       </c>
       <c r="W482" t="inlineStr">
         <is>
-          <t>重要通信,気象機関,選挙管理機関,緊急通信,電気通信事業法</t>
+          <t>重要通信|重要通信 気象機関 工事担任者</t>
         </is>
       </c>
     </row>
@@ -46779,7 +46779,7 @@
       </c>
       <c r="W483" t="inlineStr">
         <is>
-          <t>工事担任者,第二級アナログ通信,第一級アナログ通信,第二級デジタル通信,資格区分</t>
+          <t>工事担任者資格区分|工事担任者 資格区分 比較</t>
         </is>
       </c>
     </row>
@@ -46878,7 +46878,7 @@
       </c>
       <c r="W484" t="inlineStr">
         <is>
-          <t>資格者証,書換え交付,返納,10日以内,住所変更</t>
+          <t>資格者証|資格者証 書換え交付 返納 工事担任者</t>
         </is>
       </c>
     </row>
@@ -46972,7 +46972,7 @@
       </c>
       <c r="W485" t="inlineStr">
         <is>
-          <t>技術基準適合認定番号,IP移動電話端末,H,専用通信回線設備等端末,P,Q</t>
+          <t>技術基準適合認定番号|技術基準適合認定番号 工事担任者</t>
         </is>
       </c>
     </row>
@@ -47064,7 +47064,7 @@
       </c>
       <c r="W486" t="inlineStr">
         <is>
-          <t>有線電気通信法,設備の概要,変更届,届出</t>
+          <t>有線電気通信法|有線電気通信法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -47156,7 +47156,7 @@
       </c>
       <c r="W487" t="inlineStr">
         <is>
-          <t>非常事態,有線電気通信法,通信確保,使用させ,接続</t>
+          <t>有線電気通信法|有線電気通信法 非常事態 工事担任者</t>
         </is>
       </c>
     </row>
@@ -47256,7 +47256,7 @@
       </c>
       <c r="W488" t="inlineStr">
         <is>
-          <t>制御チャネル,デジタルデータ伝送用設備,総合デジタル通信用設備,端末設備等規則</t>
+          <t>制御チャネル|制御チャネル 工事担任者</t>
         </is>
       </c>
     </row>
@@ -47355,7 +47355,7 @@
       </c>
       <c r="W489" t="inlineStr">
         <is>
-          <t>分界点,識別機能,事業用電気通信設備,自営電気通信設備,漏えい</t>
+          <t>分界点|分界点 識別機能 工事担任者</t>
         </is>
       </c>
     </row>
@@ -47452,7 +47452,7 @@
       </c>
       <c r="W490" t="inlineStr">
         <is>
-          <t>絶縁抵抗,250V,2MΩ,0.2MΩ,端末設備等規則</t>
+          <t>絶縁抵抗|絶縁抵抗 250V 2MΩ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -47541,7 +47541,7 @@
       </c>
       <c r="W491" t="inlineStr">
         <is>
-          <t>配線設備,有線電気通信設備令,事業用電気通信設備,損傷,告示</t>
+          <t>有線電気通信設備令|有線電気通信設備令 工事担任者</t>
         </is>
       </c>
     </row>
@@ -47633,7 +47633,7 @@
       </c>
       <c r="W492" t="inlineStr">
         <is>
-          <t>識別符号,一の筐体,容易に開けることができない,無線設備,端末設備等規則</t>
+          <t>識別符号|識別符号 一の筐体 工事担任者</t>
         </is>
       </c>
     </row>
@@ -47725,7 +47725,7 @@
       </c>
       <c r="W493" t="inlineStr">
         <is>
-          <t>固定電話端末,通信終了メッセージ,2分以内,応答確認</t>
+          <t>固定電話端末|固定電話端末 通信終了 工事担任者</t>
         </is>
       </c>
     </row>
@@ -47825,7 +47825,7 @@
       </c>
       <c r="W494" t="inlineStr">
         <is>
-          <t>登録要求,固定電話端末,固定電話用設備,デジタルデータ伝送用設備</t>
+          <t>登録要求|登録要求 固定電話端末 工事担任者</t>
         </is>
       </c>
     </row>
@@ -47914,7 +47914,7 @@
       </c>
       <c r="W495" t="inlineStr">
         <is>
-          <t>IP移動電話端末,自動再発信,3回以内,3分,送信タイミング</t>
+          <t>IP移動電話端末|IP移動電話端末 自動再発信 工事担任者</t>
         </is>
       </c>
     </row>
@@ -48006,7 +48006,7 @@
       </c>
       <c r="W496" t="inlineStr">
         <is>
-          <t>専用通信回線設備等端末,アクセス制御,変更,管理,記録</t>
+          <t>アクセス制御|アクセス制御 変更 工事担任者</t>
         </is>
       </c>
     </row>
@@ -48106,7 +48106,7 @@
       </c>
       <c r="W497" t="inlineStr">
         <is>
-          <t>信号周波数偏差,±1.5%,ミニマムポーズ,信号送出時間,高群周波数,押しボタンダイヤル</t>
+          <t>信号周波数偏差|信号周波数偏差 工事担任者,ミニマムポーズ|ミニマムポーズ 工事担任者</t>
         </is>
       </c>
     </row>
@@ -48206,7 +48206,7 @@
       </c>
       <c r="W498" t="inlineStr">
         <is>
-          <t>絶対レベル,有効電力,1mW,デシベル,有線電気通信法</t>
+          <t>絶対レベル|絶対レベル 工事担任者</t>
         </is>
       </c>
     </row>
@@ -48295,7 +48295,7 @@
       </c>
       <c r="W499" t="inlineStr">
         <is>
-          <t>架空電線,強電流電線,支持物,30センチメートル,有線電気通信設備令</t>
+          <t>架空電線|架空電線 強電流電線 工事担任者</t>
         </is>
       </c>
     </row>
@@ -48387,7 +48387,7 @@
       </c>
       <c r="W500" t="inlineStr">
         <is>
-          <t>横断歩道橋,架空電線,3メートル,有線電気通信設備令</t>
+          <t>架空電線|架空電線 横断歩道橋 工事担任者</t>
         </is>
       </c>
     </row>
@@ -48479,7 +48479,7 @@
       </c>
       <c r="W501" t="inlineStr">
         <is>
-          <t>不正アクセス禁止法,アクセス管理者,有効性,高度化</t>
+          <t>不正アクセス禁止法|不正アクセス禁止法 工事担任者</t>
         </is>
       </c>
     </row>
@@ -48573,7 +48573,7 @@
       </c>
       <c r="W502" t="inlineStr">
         <is>
-          <t>電子署名法,真正に成立,推定,暗号化,電磁的記録</t>
+          <t>電子署名法|電子署名法 工事担任者</t>
         </is>
       </c>
     </row>
